--- a/docs/BANG DANH GIA KPI AUTO - T4 RV3.xlsx
+++ b/docs/BANG DANH GIA KPI AUTO - T4 RV3.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TienThanh\OneDrive\Tài liệu\ADE work\KPI_sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9764128E-9344-421C-94F7-83637C71C481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280A58D4-53F0-42C3-844B-3FBF14194487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lo trinh cong danh" sheetId="1" r:id="rId1"/>
     <sheet name="P2.1(Kiến Thức)" sheetId="16" r:id="rId2"/>
     <sheet name="P2.2 (Kỹ Năng chuyên Môn)" sheetId="19" r:id="rId3"/>
     <sheet name="P3.1.2 (Staff)" sheetId="23" state="hidden" r:id="rId4"/>
-    <sheet name="P3.1.2 (KPI Senior)" sheetId="25" r:id="rId5"/>
+    <sheet name="P3.1.1 (KPI Senior)" sheetId="25" r:id="rId5"/>
     <sheet name="P3.1.2 (KPI Leader)" sheetId="24" state="hidden" r:id="rId6"/>
     <sheet name="P3.1.2 (KPI Phòng Ban)" sheetId="17" r:id="rId7"/>
     <sheet name="Kết Quả Đánh Giá 3P" sheetId="6" r:id="rId8"/>
@@ -3999,20 +3999,308 @@
     <xf numFmtId="9" fontId="34" fillId="16" borderId="16" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="34" fillId="15" borderId="19" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="15" borderId="29" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="15" borderId="20" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="15" borderId="16" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="0" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="8" borderId="16" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="16" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="16" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="16" borderId="19" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="16" borderId="29" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="16" borderId="20" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="16" borderId="16" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="8" borderId="19" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="8" borderId="29" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="8" borderId="20" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="16" borderId="19" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="16" borderId="29" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="16" borderId="20" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4101,308 +4389,20 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="0" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="15" borderId="16" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="15" borderId="19" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="15" borderId="29" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="15" borderId="20" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="8" borderId="16" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="16" borderId="16" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="16" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="16" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="16" borderId="19" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="16" borderId="29" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="16" borderId="20" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="8" borderId="19" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="8" borderId="29" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="8" borderId="20" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="16" borderId="19" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="16" borderId="29" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="16" borderId="20" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -13005,10 +13005,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="275" t="s">
+      <c r="A1" s="239" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="276"/>
+      <c r="B1" s="240"/>
       <c r="C1" s="45"/>
       <c r="D1" s="12"/>
       <c r="E1" s="45"/>
@@ -13031,15 +13031,15 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="22.5" customHeight="1">
-      <c r="A2" s="277" t="s">
+      <c r="A2" s="241" t="s">
         <v>267</v>
       </c>
-      <c r="B2" s="278"/>
-      <c r="C2" s="278"/>
-      <c r="D2" s="278"/>
-      <c r="E2" s="279"/>
-      <c r="F2" s="279"/>
-      <c r="G2" s="278"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="242"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -13066,10 +13066,10 @@
       <c r="E3" s="193" t="s">
         <v>268</v>
       </c>
-      <c r="F3" s="285" t="s">
+      <c r="F3" s="249" t="s">
         <v>702</v>
       </c>
-      <c r="G3" s="285"/>
+      <c r="G3" s="249"/>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
@@ -13093,9 +13093,9 @@
       </c>
       <c r="C4" s="101"/>
       <c r="D4" s="211"/>
-      <c r="E4" s="280"/>
-      <c r="F4" s="280"/>
-      <c r="G4" s="281"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="245"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -13113,15 +13113,15 @@
       <c r="V4" s="12"/>
     </row>
     <row r="5" spans="1:22" ht="31.5" customHeight="1" thickBot="1">
-      <c r="A5" s="282" t="s">
+      <c r="A5" s="246" t="s">
         <v>315</v>
       </c>
-      <c r="B5" s="283"/>
-      <c r="C5" s="283"/>
-      <c r="D5" s="283"/>
-      <c r="E5" s="283"/>
-      <c r="F5" s="283"/>
-      <c r="G5" s="284"/>
+      <c r="B5" s="247"/>
+      <c r="C5" s="247"/>
+      <c r="D5" s="247"/>
+      <c r="E5" s="247"/>
+      <c r="F5" s="247"/>
+      <c r="G5" s="248"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
@@ -22217,84 +22217,84 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="B2" s="292"/>
-      <c r="C2" s="292"/>
-      <c r="D2" s="296" t="s">
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="262" t="s">
         <v>669</v>
       </c>
-      <c r="E2" s="297"/>
-      <c r="F2" s="297"/>
-      <c r="G2" s="297"/>
-      <c r="H2" s="297"/>
-      <c r="I2" s="297"/>
-      <c r="J2" s="297"/>
-      <c r="K2" s="297"/>
-      <c r="L2" s="297"/>
-      <c r="M2" s="297"/>
-      <c r="N2" s="297"/>
-      <c r="O2" s="297"/>
-      <c r="P2" s="297"/>
-      <c r="Q2" s="297"/>
-      <c r="R2" s="297"/>
-      <c r="S2" s="297"/>
-      <c r="T2" s="290" t="s">
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="263"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
+      <c r="M2" s="263"/>
+      <c r="N2" s="263"/>
+      <c r="O2" s="263"/>
+      <c r="P2" s="263"/>
+      <c r="Q2" s="263"/>
+      <c r="R2" s="263"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="256" t="s">
         <v>670</v>
       </c>
-      <c r="U2" s="291"/>
-      <c r="V2" s="292"/>
-      <c r="W2" s="292"/>
+      <c r="U2" s="257"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="B3" s="292"/>
-      <c r="C3" s="292"/>
-      <c r="D3" s="297"/>
-      <c r="E3" s="297"/>
-      <c r="F3" s="297"/>
-      <c r="G3" s="297"/>
-      <c r="H3" s="297"/>
-      <c r="I3" s="297"/>
-      <c r="J3" s="297"/>
-      <c r="K3" s="297"/>
-      <c r="L3" s="297"/>
-      <c r="M3" s="297"/>
-      <c r="N3" s="297"/>
-      <c r="O3" s="297"/>
-      <c r="P3" s="297"/>
-      <c r="Q3" s="297"/>
-      <c r="R3" s="297"/>
-      <c r="S3" s="297"/>
+      <c r="B3" s="258"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="263"/>
+      <c r="H3" s="263"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="M3" s="263"/>
+      <c r="N3" s="263"/>
+      <c r="O3" s="263"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
       <c r="T3" s="183" t="s">
         <v>671</v>
       </c>
       <c r="U3" s="183"/>
-      <c r="V3" s="292"/>
-      <c r="W3" s="292"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="B4" s="292"/>
-      <c r="C4" s="292"/>
-      <c r="D4" s="297"/>
-      <c r="E4" s="297"/>
-      <c r="F4" s="297"/>
-      <c r="G4" s="297"/>
-      <c r="H4" s="297"/>
-      <c r="I4" s="297"/>
-      <c r="J4" s="297"/>
-      <c r="K4" s="297"/>
-      <c r="L4" s="297"/>
-      <c r="M4" s="297"/>
-      <c r="N4" s="297"/>
-      <c r="O4" s="297"/>
-      <c r="P4" s="297"/>
-      <c r="Q4" s="297"/>
-      <c r="R4" s="297"/>
-      <c r="S4" s="297"/>
+      <c r="B4" s="258"/>
+      <c r="C4" s="258"/>
+      <c r="D4" s="263"/>
+      <c r="E4" s="263"/>
+      <c r="F4" s="263"/>
+      <c r="G4" s="263"/>
+      <c r="H4" s="263"/>
+      <c r="I4" s="263"/>
+      <c r="J4" s="263"/>
+      <c r="K4" s="263"/>
+      <c r="L4" s="263"/>
+      <c r="M4" s="263"/>
+      <c r="N4" s="263"/>
+      <c r="O4" s="263"/>
+      <c r="P4" s="263"/>
+      <c r="Q4" s="263"/>
+      <c r="R4" s="263"/>
+      <c r="S4" s="263"/>
       <c r="T4" s="183" t="s">
         <v>672</v>
       </c>
       <c r="U4" s="183"/>
-      <c r="V4" s="292"/>
-      <c r="W4" s="292"/>
+      <c r="V4" s="258"/>
+      <c r="W4" s="258"/>
     </row>
     <row r="6" spans="1:26">
       <c r="H6" s="184" t="s">
@@ -22308,47 +22308,47 @@
       </c>
     </row>
     <row r="9" spans="1:26" s="45" customFormat="1" ht="15" customHeight="1">
-      <c r="B9" s="293" t="s">
+      <c r="B9" s="259" t="s">
         <v>673</v>
       </c>
-      <c r="C9" s="294" t="s">
+      <c r="C9" s="260" t="s">
         <v>674</v>
       </c>
-      <c r="D9" s="294" t="s">
+      <c r="D9" s="260" t="s">
         <v>675</v>
       </c>
-      <c r="E9" s="293" t="s">
+      <c r="E9" s="259" t="s">
         <v>676</v>
       </c>
-      <c r="F9" s="293"/>
-      <c r="G9" s="293"/>
-      <c r="H9" s="293"/>
-      <c r="I9" s="293"/>
-      <c r="J9" s="293"/>
-      <c r="K9" s="293"/>
-      <c r="L9" s="293"/>
-      <c r="M9" s="293"/>
-      <c r="N9" s="293"/>
-      <c r="O9" s="293"/>
-      <c r="P9" s="293"/>
-      <c r="Q9" s="293"/>
-      <c r="R9" s="293"/>
-      <c r="S9" s="293"/>
-      <c r="T9" s="293"/>
-      <c r="U9" s="294" t="s">
+      <c r="F9" s="259"/>
+      <c r="G9" s="259"/>
+      <c r="H9" s="259"/>
+      <c r="I9" s="259"/>
+      <c r="J9" s="259"/>
+      <c r="K9" s="259"/>
+      <c r="L9" s="259"/>
+      <c r="M9" s="259"/>
+      <c r="N9" s="259"/>
+      <c r="O9" s="259"/>
+      <c r="P9" s="259"/>
+      <c r="Q9" s="259"/>
+      <c r="R9" s="259"/>
+      <c r="S9" s="259"/>
+      <c r="T9" s="259"/>
+      <c r="U9" s="260" t="s">
         <v>677</v>
       </c>
-      <c r="V9" s="294" t="s">
+      <c r="V9" s="260" t="s">
         <v>678</v>
       </c>
-      <c r="W9" s="294" t="s">
+      <c r="W9" s="260" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="45" customFormat="1">
-      <c r="B10" s="293"/>
-      <c r="C10" s="294"/>
-      <c r="D10" s="294"/>
+      <c r="B10" s="259"/>
+      <c r="C10" s="260"/>
+      <c r="D10" s="260"/>
       <c r="E10" s="185">
         <v>1</v>
       </c>
@@ -22397,14 +22397,14 @@
       <c r="T10" s="185">
         <v>16</v>
       </c>
-      <c r="U10" s="293"/>
-      <c r="V10" s="293"/>
-      <c r="W10" s="293"/>
+      <c r="U10" s="259"/>
+      <c r="V10" s="259"/>
+      <c r="W10" s="259"/>
     </row>
     <row r="11" spans="1:26" s="45" customFormat="1" ht="159" customHeight="1">
-      <c r="B11" s="293"/>
-      <c r="C11" s="294"/>
-      <c r="D11" s="294"/>
+      <c r="B11" s="259"/>
+      <c r="C11" s="260"/>
+      <c r="D11" s="260"/>
       <c r="E11" s="186" t="s">
         <v>680</v>
       </c>
@@ -22453,14 +22453,14 @@
       <c r="T11" s="186" t="s">
         <v>695</v>
       </c>
-      <c r="U11" s="293"/>
-      <c r="V11" s="293"/>
-      <c r="W11" s="293"/>
+      <c r="U11" s="259"/>
+      <c r="V11" s="259"/>
+      <c r="W11" s="259"/>
     </row>
     <row r="12" spans="1:26" s="101" customFormat="1" ht="15" customHeight="1">
-      <c r="B12" s="293"/>
-      <c r="C12" s="295"/>
-      <c r="D12" s="295"/>
+      <c r="B12" s="259"/>
+      <c r="C12" s="261"/>
+      <c r="D12" s="261"/>
       <c r="E12" s="202">
         <v>8</v>
       </c>
@@ -22518,7 +22518,7 @@
     </row>
     <row r="13" spans="1:26" customFormat="1">
       <c r="A13" s="198"/>
-      <c r="B13" s="286">
+      <c r="B13" s="253">
         <v>1</v>
       </c>
       <c r="C13" s="218" t="s">
@@ -22603,7 +22603,7 @@
     </row>
     <row r="14" spans="1:26" customFormat="1">
       <c r="A14" s="198"/>
-      <c r="B14" s="287"/>
+      <c r="B14" s="254"/>
       <c r="C14" s="221"/>
       <c r="D14" s="222" t="s">
         <v>696</v>
@@ -22633,7 +22633,7 @@
     </row>
     <row r="15" spans="1:26" customFormat="1">
       <c r="A15" s="198"/>
-      <c r="B15" s="288"/>
+      <c r="B15" s="255"/>
       <c r="C15" s="224" t="s">
         <v>702</v>
       </c>
@@ -22716,7 +22716,7 @@
     </row>
     <row r="16" spans="1:26" customFormat="1" ht="14.25" customHeight="1">
       <c r="A16" s="198"/>
-      <c r="B16" s="286">
+      <c r="B16" s="253">
         <v>2</v>
       </c>
       <c r="C16" s="218" t="s">
@@ -22801,7 +22801,7 @@
     </row>
     <row r="17" spans="1:26" customFormat="1" ht="14.25" customHeight="1">
       <c r="A17" s="198"/>
-      <c r="B17" s="287"/>
+      <c r="B17" s="254"/>
       <c r="C17" s="221"/>
       <c r="D17" s="222" t="s">
         <v>696</v>
@@ -22831,7 +22831,7 @@
     </row>
     <row r="18" spans="1:26" customFormat="1" ht="14.25" customHeight="1">
       <c r="A18" s="198"/>
-      <c r="B18" s="288"/>
+      <c r="B18" s="255"/>
       <c r="C18" s="224" t="s">
         <v>702</v>
       </c>
@@ -22937,50 +22937,45 @@
       <c r="W19" s="196"/>
     </row>
     <row r="20" spans="1:26">
-      <c r="P20" s="299" t="s">
+      <c r="P20" s="252" t="s">
         <v>743</v>
       </c>
-      <c r="Q20" s="299"/>
-      <c r="R20" s="299"/>
-      <c r="S20" s="299"/>
+      <c r="Q20" s="252"/>
+      <c r="R20" s="252"/>
+      <c r="S20" s="252"/>
     </row>
     <row r="21" spans="1:26">
-      <c r="D21" s="289" t="s">
+      <c r="D21" s="250" t="s">
         <v>698</v>
       </c>
-      <c r="E21" s="289"/>
-      <c r="P21" s="298" t="s">
+      <c r="E21" s="250"/>
+      <c r="P21" s="251" t="s">
         <v>699</v>
       </c>
-      <c r="Q21" s="298"/>
-      <c r="R21" s="298"/>
-      <c r="S21" s="298"/>
+      <c r="Q21" s="251"/>
+      <c r="R21" s="251"/>
+      <c r="S21" s="251"/>
     </row>
     <row r="22" spans="1:26">
-      <c r="D22" s="299" t="s">
+      <c r="D22" s="252" t="s">
         <v>700</v>
       </c>
-      <c r="E22" s="299"/>
+      <c r="E22" s="252"/>
     </row>
     <row r="23" spans="1:26">
-      <c r="D23" s="299" t="s">
+      <c r="D23" s="252" t="s">
         <v>701</v>
       </c>
-      <c r="E23" s="299"/>
+      <c r="E23" s="252"/>
     </row>
     <row r="27" spans="1:26">
-      <c r="D27" s="289" t="s">
+      <c r="D27" s="250" t="s">
         <v>702</v>
       </c>
-      <c r="E27" s="289"/>
+      <c r="E27" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="B16:B18"/>
     <mergeCell ref="D21:E21"/>
@@ -22997,6 +22992,11 @@
     <mergeCell ref="W9:W11"/>
     <mergeCell ref="B2:C4"/>
     <mergeCell ref="D2:S4"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23025,52 +23025,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="319"/>
-      <c r="B1" s="319"/>
-      <c r="C1" s="322" t="s">
+      <c r="A1" s="268"/>
+      <c r="B1" s="268"/>
+      <c r="C1" s="271" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="324" t="s">
+      <c r="D1" s="273" t="s">
         <v>731</v>
       </c>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325"/>
-      <c r="G1" s="325"/>
-      <c r="H1" s="326"/>
+      <c r="E1" s="274"/>
+      <c r="F1" s="274"/>
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1">
-      <c r="A2" s="320"/>
-      <c r="B2" s="320"/>
-      <c r="C2" s="323"/>
-      <c r="D2" s="327"/>
-      <c r="E2" s="328"/>
-      <c r="F2" s="328"/>
-      <c r="G2" s="328"/>
-      <c r="H2" s="329"/>
+      <c r="A2" s="269"/>
+      <c r="B2" s="269"/>
+      <c r="C2" s="272"/>
+      <c r="D2" s="276"/>
+      <c r="E2" s="277"/>
+      <c r="F2" s="277"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="320"/>
-      <c r="B3" s="320"/>
+      <c r="A3" s="269"/>
+      <c r="B3" s="269"/>
       <c r="C3" s="53" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="320"/>
-      <c r="B4" s="320"/>
+      <c r="A4" s="269"/>
+      <c r="B4" s="269"/>
       <c r="C4" s="55" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75">
-      <c r="A5" s="321"/>
-      <c r="B5" s="321"/>
+      <c r="A5" s="270"/>
+      <c r="B5" s="270"/>
       <c r="C5" s="144"/>
       <c r="D5" s="145"/>
       <c r="E5" s="145"/>
@@ -23084,73 +23084,73 @@
       <c r="M5" s="145"/>
     </row>
     <row r="6" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A6" s="315" t="s">
+      <c r="A6" s="267" t="s">
         <v>405</v>
       </c>
-      <c r="B6" s="315" t="s">
+      <c r="B6" s="267" t="s">
         <v>321</v>
       </c>
-      <c r="C6" s="315" t="s">
+      <c r="C6" s="267" t="s">
         <v>322</v>
       </c>
-      <c r="D6" s="315" t="s">
+      <c r="D6" s="267" t="s">
         <v>289</v>
       </c>
-      <c r="E6" s="315" t="s">
+      <c r="E6" s="267" t="s">
         <v>323</v>
       </c>
-      <c r="F6" s="315" t="s">
+      <c r="F6" s="267" t="s">
         <v>324</v>
       </c>
-      <c r="G6" s="315" t="s">
+      <c r="G6" s="267" t="s">
         <v>416</v>
       </c>
       <c r="H6" s="147"/>
-      <c r="I6" s="315" t="s">
+      <c r="I6" s="267" t="s">
         <v>326</v>
       </c>
-      <c r="J6" s="315" t="s">
+      <c r="J6" s="267" t="s">
         <v>327</v>
       </c>
-      <c r="K6" s="315" t="s">
+      <c r="K6" s="267" t="s">
         <v>328</v>
       </c>
-      <c r="L6" s="315" t="s">
+      <c r="L6" s="267" t="s">
         <v>493</v>
       </c>
-      <c r="M6" s="315"/>
+      <c r="M6" s="267"/>
     </row>
     <row r="7" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A7" s="315"/>
-      <c r="B7" s="315"/>
-      <c r="C7" s="315"/>
-      <c r="D7" s="315"/>
-      <c r="E7" s="315"/>
-      <c r="F7" s="315"/>
-      <c r="G7" s="315"/>
+      <c r="A7" s="267"/>
+      <c r="B7" s="267"/>
+      <c r="C7" s="267"/>
+      <c r="D7" s="267"/>
+      <c r="E7" s="267"/>
+      <c r="F7" s="267"/>
+      <c r="G7" s="267"/>
       <c r="H7" s="147"/>
-      <c r="I7" s="315"/>
-      <c r="J7" s="315"/>
-      <c r="K7" s="315"/>
-      <c r="L7" s="315" t="s">
+      <c r="I7" s="267"/>
+      <c r="J7" s="267"/>
+      <c r="K7" s="267"/>
+      <c r="L7" s="267" t="s">
         <v>718</v>
       </c>
-      <c r="M7" s="315"/>
+      <c r="M7" s="267"/>
     </row>
     <row r="8" spans="1:13" s="57" customFormat="1" ht="31.5">
-      <c r="A8" s="315"/>
-      <c r="B8" s="315"/>
-      <c r="C8" s="315"/>
-      <c r="D8" s="315"/>
-      <c r="E8" s="315"/>
-      <c r="F8" s="315"/>
-      <c r="G8" s="315"/>
+      <c r="A8" s="267"/>
+      <c r="B8" s="267"/>
+      <c r="C8" s="267"/>
+      <c r="D8" s="267"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="267"/>
       <c r="H8" s="69" t="s">
         <v>325</v>
       </c>
-      <c r="I8" s="315"/>
-      <c r="J8" s="315"/>
-      <c r="K8" s="315"/>
+      <c r="I8" s="267"/>
+      <c r="J8" s="267"/>
+      <c r="K8" s="267"/>
       <c r="L8" s="70" t="s">
         <v>292</v>
       </c>
@@ -23159,14 +23159,14 @@
       </c>
     </row>
     <row r="9" spans="1:13" s="57" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A9" s="330" t="s">
+      <c r="A9" s="279" t="s">
         <v>415</v>
       </c>
-      <c r="B9" s="330"/>
-      <c r="C9" s="330"/>
-      <c r="D9" s="330"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
+      <c r="B9" s="279"/>
+      <c r="C9" s="279"/>
+      <c r="D9" s="279"/>
+      <c r="E9" s="279"/>
+      <c r="F9" s="279"/>
       <c r="G9" s="148">
         <f>SUM(G10:G26)</f>
         <v>1</v>
@@ -23185,10 +23185,10 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="58" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A10" s="301" t="s">
+      <c r="A10" s="281" t="s">
         <v>290</v>
       </c>
-      <c r="B10" s="302" t="s">
+      <c r="B10" s="282" t="s">
         <v>332</v>
       </c>
       <c r="C10" s="98" t="s">
@@ -23197,13 +23197,13 @@
       <c r="D10" s="103" t="s">
         <v>459</v>
       </c>
-      <c r="E10" s="303" t="s">
+      <c r="E10" s="283" t="s">
         <v>396</v>
       </c>
       <c r="F10" s="103" t="s">
         <v>334</v>
       </c>
-      <c r="G10" s="304">
+      <c r="G10" s="280">
         <v>0.15</v>
       </c>
       <c r="H10" s="62"/>
@@ -23219,25 +23219,25 @@
       <c r="L10" s="78">
         <v>0</v>
       </c>
-      <c r="M10" s="316">
+      <c r="M10" s="264">
         <f>IF(SUM(L10:L12)&gt;=1,$G$10,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="58" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A11" s="301"/>
-      <c r="B11" s="302"/>
+      <c r="A11" s="281"/>
+      <c r="B11" s="282"/>
       <c r="C11" s="97" t="s">
         <v>486</v>
       </c>
       <c r="D11" s="103" t="s">
         <v>458</v>
       </c>
-      <c r="E11" s="303"/>
+      <c r="E11" s="283"/>
       <c r="F11" s="77" t="s">
         <v>476</v>
       </c>
-      <c r="G11" s="304"/>
+      <c r="G11" s="280"/>
       <c r="H11" s="62"/>
       <c r="I11" s="87" t="s">
         <v>335</v>
@@ -23249,11 +23249,11 @@
         <v>335</v>
       </c>
       <c r="L11" s="78"/>
-      <c r="M11" s="317"/>
+      <c r="M11" s="265"/>
     </row>
     <row r="12" spans="1:13" s="58" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A12" s="301"/>
-      <c r="B12" s="303" t="s">
+      <c r="A12" s="281"/>
+      <c r="B12" s="283" t="s">
         <v>343</v>
       </c>
       <c r="C12" s="97" t="s">
@@ -23262,11 +23262,11 @@
       <c r="D12" s="103" t="s">
         <v>280</v>
       </c>
-      <c r="E12" s="303"/>
+      <c r="E12" s="283"/>
       <c r="F12" s="77" t="s">
         <v>411</v>
       </c>
-      <c r="G12" s="304"/>
+      <c r="G12" s="280"/>
       <c r="H12" s="66"/>
       <c r="I12" s="87" t="s">
         <v>335</v>
@@ -23280,22 +23280,22 @@
       <c r="L12" s="96">
         <v>0</v>
       </c>
-      <c r="M12" s="317"/>
+      <c r="M12" s="265"/>
     </row>
     <row r="13" spans="1:13" s="58" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A13" s="301"/>
-      <c r="B13" s="302"/>
+      <c r="A13" s="281"/>
+      <c r="B13" s="282"/>
       <c r="C13" s="97" t="s">
         <v>460</v>
       </c>
       <c r="D13" s="77" t="s">
         <v>461</v>
       </c>
-      <c r="E13" s="303"/>
+      <c r="E13" s="283"/>
       <c r="F13" s="77" t="s">
         <v>477</v>
       </c>
-      <c r="G13" s="304"/>
+      <c r="G13" s="280"/>
       <c r="H13" s="66"/>
       <c r="I13" s="87" t="s">
         <v>335</v>
@@ -23307,10 +23307,10 @@
         <v>335</v>
       </c>
       <c r="L13" s="96"/>
-      <c r="M13" s="318"/>
+      <c r="M13" s="266"/>
     </row>
     <row r="14" spans="1:13" s="59" customFormat="1" ht="78" customHeight="1">
-      <c r="A14" s="305" t="s">
+      <c r="A14" s="285" t="s">
         <v>281</v>
       </c>
       <c r="B14" s="113" t="s">
@@ -23322,13 +23322,13 @@
       <c r="D14" s="113" t="s">
         <v>316</v>
       </c>
-      <c r="E14" s="308" t="s">
+      <c r="E14" s="286" t="s">
         <v>397</v>
       </c>
       <c r="F14" s="113" t="s">
         <v>404</v>
       </c>
-      <c r="G14" s="310">
+      <c r="G14" s="288">
         <v>0.2</v>
       </c>
       <c r="H14" s="107"/>
@@ -23344,13 +23344,13 @@
       <c r="L14" s="95">
         <v>0</v>
       </c>
-      <c r="M14" s="312">
+      <c r="M14" s="284">
         <f>IF(SUM(L14:L15)&gt;=1,$G$14,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="58" customFormat="1" ht="51">
-      <c r="A15" s="305"/>
+      <c r="A15" s="285"/>
       <c r="B15" s="113" t="s">
         <v>407</v>
       </c>
@@ -23360,11 +23360,11 @@
       <c r="D15" s="113" t="s">
         <v>409</v>
       </c>
-      <c r="E15" s="309"/>
+      <c r="E15" s="287"/>
       <c r="F15" s="113" t="s">
         <v>410</v>
       </c>
-      <c r="G15" s="310"/>
+      <c r="G15" s="288"/>
       <c r="H15" s="107"/>
       <c r="I15" s="88" t="s">
         <v>348</v>
@@ -23378,13 +23378,13 @@
       <c r="L15" s="95">
         <v>0</v>
       </c>
-      <c r="M15" s="312"/>
+      <c r="M15" s="284"/>
     </row>
     <row r="16" spans="1:13" s="58" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A16" s="301" t="s">
+      <c r="A16" s="281" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="313" t="s">
+      <c r="B16" s="289" t="s">
         <v>351</v>
       </c>
       <c r="C16" s="103" t="s">
@@ -23393,13 +23393,13 @@
       <c r="D16" s="77" t="s">
         <v>472</v>
       </c>
-      <c r="E16" s="303" t="s">
+      <c r="E16" s="283" t="s">
         <v>398</v>
       </c>
       <c r="F16" s="103" t="s">
         <v>353</v>
       </c>
-      <c r="G16" s="304">
+      <c r="G16" s="280">
         <v>0.15</v>
       </c>
       <c r="H16" s="105"/>
@@ -23415,25 +23415,25 @@
       <c r="L16" s="96">
         <v>0</v>
       </c>
-      <c r="M16" s="312">
+      <c r="M16" s="284">
         <f>IF(SUM(L16:L18)&gt;=1,$G$16,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="58" customFormat="1" ht="39.6" hidden="1" customHeight="1">
-      <c r="A17" s="301"/>
-      <c r="B17" s="313"/>
-      <c r="C17" s="314" t="s">
+      <c r="A17" s="281"/>
+      <c r="B17" s="289"/>
+      <c r="C17" s="290" t="s">
         <v>356</v>
       </c>
       <c r="D17" s="77" t="s">
         <v>473</v>
       </c>
-      <c r="E17" s="302"/>
+      <c r="E17" s="282"/>
       <c r="F17" s="77" t="s">
         <v>474</v>
       </c>
-      <c r="G17" s="304"/>
+      <c r="G17" s="280"/>
       <c r="H17" s="105"/>
       <c r="I17" s="99">
         <v>1</v>
@@ -23447,20 +23447,20 @@
       <c r="L17" s="96">
         <v>0</v>
       </c>
-      <c r="M17" s="312"/>
+      <c r="M17" s="284"/>
     </row>
     <row r="18" spans="1:13" s="58" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A18" s="301"/>
-      <c r="B18" s="313"/>
-      <c r="C18" s="314"/>
+      <c r="A18" s="281"/>
+      <c r="B18" s="289"/>
+      <c r="C18" s="290"/>
       <c r="D18" s="77" t="s">
         <v>478</v>
       </c>
-      <c r="E18" s="302"/>
+      <c r="E18" s="282"/>
       <c r="F18" s="103" t="s">
         <v>364</v>
       </c>
-      <c r="G18" s="304"/>
+      <c r="G18" s="280"/>
       <c r="H18" s="105"/>
       <c r="I18" s="105">
         <v>0</v>
@@ -23474,28 +23474,28 @@
       <c r="L18" s="96">
         <v>0</v>
       </c>
-      <c r="M18" s="312"/>
+      <c r="M18" s="284"/>
     </row>
     <row r="19" spans="1:13" s="58" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A19" s="305" t="s">
+      <c r="A19" s="285" t="s">
         <v>282</v>
       </c>
-      <c r="B19" s="309" t="s">
+      <c r="B19" s="287" t="s">
         <v>365</v>
       </c>
-      <c r="C19" s="307" t="s">
+      <c r="C19" s="291" t="s">
         <v>463</v>
       </c>
       <c r="D19" s="113" t="s">
         <v>406</v>
       </c>
-      <c r="E19" s="308" t="s">
+      <c r="E19" s="286" t="s">
         <v>399</v>
       </c>
       <c r="F19" s="113" t="s">
         <v>479</v>
       </c>
-      <c r="G19" s="310">
+      <c r="G19" s="288">
         <v>0.15</v>
       </c>
       <c r="H19" s="107"/>
@@ -23511,23 +23511,23 @@
       <c r="L19" s="95">
         <v>0</v>
       </c>
-      <c r="M19" s="312">
+      <c r="M19" s="284">
         <f>IF(SUM(L19:L20)&gt;=1,$G$19,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="58" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A20" s="305"/>
-      <c r="B20" s="309"/>
-      <c r="C20" s="306"/>
+      <c r="A20" s="285"/>
+      <c r="B20" s="287"/>
+      <c r="C20" s="292"/>
       <c r="D20" s="113" t="s">
         <v>464</v>
       </c>
-      <c r="E20" s="309"/>
+      <c r="E20" s="287"/>
       <c r="F20" s="108" t="s">
         <v>369</v>
       </c>
-      <c r="G20" s="310"/>
+      <c r="G20" s="288"/>
       <c r="H20" s="107"/>
       <c r="I20" s="107" t="s">
         <v>368</v>
@@ -23541,28 +23541,28 @@
       <c r="L20" s="95">
         <v>0</v>
       </c>
-      <c r="M20" s="312"/>
+      <c r="M20" s="284"/>
     </row>
     <row r="21" spans="1:13" ht="39.6" customHeight="1">
-      <c r="A21" s="301" t="s">
+      <c r="A21" s="281" t="s">
         <v>283</v>
       </c>
-      <c r="B21" s="302" t="s">
+      <c r="B21" s="282" t="s">
         <v>370</v>
       </c>
-      <c r="C21" s="311" t="s">
+      <c r="C21" s="294" t="s">
         <v>462</v>
       </c>
       <c r="D21" s="77" t="s">
         <v>482</v>
       </c>
-      <c r="E21" s="303" t="s">
+      <c r="E21" s="283" t="s">
         <v>400</v>
       </c>
       <c r="F21" s="77" t="s">
         <v>483</v>
       </c>
-      <c r="G21" s="304">
+      <c r="G21" s="280">
         <v>0.15</v>
       </c>
       <c r="H21" s="105"/>
@@ -23578,23 +23578,23 @@
       <c r="L21" s="96">
         <v>0</v>
       </c>
-      <c r="M21" s="300">
+      <c r="M21" s="293">
         <f>IF(SUM(L21:L22)&gt;=1,$G$21,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="39.6" customHeight="1">
-      <c r="A22" s="301"/>
-      <c r="B22" s="302"/>
-      <c r="C22" s="311"/>
+      <c r="A22" s="281"/>
+      <c r="B22" s="282"/>
+      <c r="C22" s="294"/>
       <c r="D22" s="77" t="s">
         <v>484</v>
       </c>
-      <c r="E22" s="302"/>
+      <c r="E22" s="282"/>
       <c r="F22" s="103" t="s">
         <v>375</v>
       </c>
-      <c r="G22" s="304"/>
+      <c r="G22" s="280"/>
       <c r="H22" s="105"/>
       <c r="I22" s="71">
         <v>0.01</v>
@@ -23608,28 +23608,28 @@
       <c r="L22" s="96">
         <v>0</v>
       </c>
-      <c r="M22" s="300"/>
+      <c r="M22" s="293"/>
     </row>
     <row r="23" spans="1:13" ht="39.6" customHeight="1">
-      <c r="A23" s="305" t="s">
+      <c r="A23" s="285" t="s">
         <v>291</v>
       </c>
-      <c r="B23" s="306" t="s">
+      <c r="B23" s="292" t="s">
         <v>378</v>
       </c>
-      <c r="C23" s="307" t="s">
+      <c r="C23" s="291" t="s">
         <v>465</v>
       </c>
       <c r="D23" s="113" t="s">
         <v>466</v>
       </c>
-      <c r="E23" s="308" t="s">
+      <c r="E23" s="286" t="s">
         <v>401</v>
       </c>
       <c r="F23" s="108" t="s">
         <v>381</v>
       </c>
-      <c r="G23" s="310">
+      <c r="G23" s="288">
         <v>0.15</v>
       </c>
       <c r="H23" s="74"/>
@@ -23645,23 +23645,23 @@
       <c r="L23" s="79">
         <v>0</v>
       </c>
-      <c r="M23" s="300">
+      <c r="M23" s="293">
         <f>IF(SUM(L23:L25)&gt;=1,$G$23,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="39.6" customHeight="1">
-      <c r="A24" s="305"/>
-      <c r="B24" s="306"/>
-      <c r="C24" s="306"/>
+      <c r="A24" s="285"/>
+      <c r="B24" s="292"/>
+      <c r="C24" s="292"/>
       <c r="D24" s="113" t="s">
         <v>467</v>
       </c>
-      <c r="E24" s="309"/>
+      <c r="E24" s="287"/>
       <c r="F24" s="108" t="s">
         <v>385</v>
       </c>
-      <c r="G24" s="310"/>
+      <c r="G24" s="288"/>
       <c r="H24" s="107"/>
       <c r="I24" s="107" t="s">
         <v>382</v>
@@ -23675,10 +23675,10 @@
       <c r="L24" s="79">
         <v>0</v>
       </c>
-      <c r="M24" s="300"/>
+      <c r="M24" s="293"/>
     </row>
     <row r="25" spans="1:13" ht="39.6" customHeight="1">
-      <c r="A25" s="305"/>
+      <c r="A25" s="285"/>
       <c r="B25" s="108" t="s">
         <v>386</v>
       </c>
@@ -23688,11 +23688,11 @@
       <c r="D25" s="113" t="s">
         <v>468</v>
       </c>
-      <c r="E25" s="309"/>
+      <c r="E25" s="287"/>
       <c r="F25" s="108" t="s">
         <v>387</v>
       </c>
-      <c r="G25" s="310"/>
+      <c r="G25" s="288"/>
       <c r="H25" s="107"/>
       <c r="I25" s="76" t="s">
         <v>388</v>
@@ -23706,7 +23706,7 @@
       <c r="L25" s="79">
         <v>0</v>
       </c>
-      <c r="M25" s="300"/>
+      <c r="M25" s="293"/>
     </row>
     <row r="26" spans="1:13" ht="70.900000000000006" customHeight="1">
       <c r="A26" s="102" t="s">
@@ -23753,6 +23753,40 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="M23:M25"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="M16:M18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="E10:E13"/>
     <mergeCell ref="M10:M13"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="L6:M6"/>
@@ -23769,40 +23803,6 @@
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="M16:M18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="M23:M25"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C21:C22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -23833,52 +23833,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20.25">
-      <c r="A1" s="319"/>
-      <c r="B1" s="319"/>
-      <c r="C1" s="322" t="s">
+      <c r="A1" s="268"/>
+      <c r="B1" s="268"/>
+      <c r="C1" s="271" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="324" t="s">
+      <c r="D1" s="273" t="s">
         <v>744</v>
       </c>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325"/>
-      <c r="G1" s="325"/>
-      <c r="H1" s="326"/>
+      <c r="E1" s="274"/>
+      <c r="F1" s="274"/>
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
       <c r="I1" s="187"/>
       <c r="J1" s="187"/>
       <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:15" ht="20.25">
-      <c r="A2" s="320"/>
-      <c r="B2" s="320"/>
-      <c r="C2" s="323"/>
-      <c r="D2" s="327"/>
-      <c r="E2" s="328"/>
-      <c r="F2" s="328"/>
-      <c r="G2" s="328"/>
-      <c r="H2" s="329"/>
+      <c r="A2" s="269"/>
+      <c r="B2" s="269"/>
+      <c r="C2" s="272"/>
+      <c r="D2" s="276"/>
+      <c r="E2" s="277"/>
+      <c r="F2" s="277"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278"/>
       <c r="I2" s="187"/>
       <c r="J2" s="187"/>
       <c r="K2" s="187"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="320"/>
-      <c r="B3" s="320"/>
+      <c r="A3" s="269"/>
+      <c r="B3" s="269"/>
       <c r="C3" s="53" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="320"/>
-      <c r="B4" s="320"/>
+      <c r="A4" s="269"/>
+      <c r="B4" s="269"/>
       <c r="C4" s="55" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75">
-      <c r="A5" s="321"/>
-      <c r="B5" s="321"/>
+      <c r="A5" s="270"/>
+      <c r="B5" s="270"/>
       <c r="C5" s="144"/>
       <c r="D5" s="145"/>
       <c r="E5" s="145"/>
@@ -23894,81 +23894,81 @@
       <c r="O5" s="145"/>
     </row>
     <row r="6" spans="1:15" ht="15.75">
-      <c r="A6" s="315" t="s">
+      <c r="A6" s="267" t="s">
         <v>405</v>
       </c>
-      <c r="B6" s="315" t="s">
+      <c r="B6" s="267" t="s">
         <v>321</v>
       </c>
-      <c r="C6" s="315" t="s">
+      <c r="C6" s="267" t="s">
         <v>322</v>
       </c>
-      <c r="D6" s="315" t="s">
+      <c r="D6" s="267" t="s">
         <v>289</v>
       </c>
-      <c r="E6" s="315" t="s">
+      <c r="E6" s="267" t="s">
         <v>323</v>
       </c>
-      <c r="F6" s="315" t="s">
+      <c r="F6" s="267" t="s">
         <v>324</v>
       </c>
-      <c r="G6" s="315" t="s">
+      <c r="G6" s="267" t="s">
         <v>416</v>
       </c>
       <c r="H6" s="147"/>
-      <c r="I6" s="315" t="s">
+      <c r="I6" s="267" t="s">
         <v>732</v>
       </c>
-      <c r="J6" s="315" t="s">
+      <c r="J6" s="267" t="s">
         <v>327</v>
       </c>
-      <c r="K6" s="315" t="s">
+      <c r="K6" s="267" t="s">
         <v>328</v>
       </c>
-      <c r="L6" s="315" t="s">
+      <c r="L6" s="267" t="s">
         <v>414</v>
       </c>
-      <c r="M6" s="315"/>
-      <c r="N6" s="315" t="s">
+      <c r="M6" s="267"/>
+      <c r="N6" s="267" t="s">
         <v>414</v>
       </c>
-      <c r="O6" s="315"/>
+      <c r="O6" s="267"/>
     </row>
     <row r="7" spans="1:15" ht="15.75">
-      <c r="A7" s="315"/>
-      <c r="B7" s="315"/>
-      <c r="C7" s="315"/>
-      <c r="D7" s="315"/>
-      <c r="E7" s="315"/>
-      <c r="F7" s="315"/>
-      <c r="G7" s="315"/>
+      <c r="A7" s="267"/>
+      <c r="B7" s="267"/>
+      <c r="C7" s="267"/>
+      <c r="D7" s="267"/>
+      <c r="E7" s="267"/>
+      <c r="F7" s="267"/>
+      <c r="G7" s="267"/>
       <c r="H7" s="147"/>
-      <c r="I7" s="315"/>
-      <c r="J7" s="315"/>
-      <c r="K7" s="315"/>
-      <c r="L7" s="315" t="s">
+      <c r="I7" s="267"/>
+      <c r="J7" s="267"/>
+      <c r="K7" s="267"/>
+      <c r="L7" s="267" t="s">
         <v>418</v>
       </c>
-      <c r="M7" s="315"/>
-      <c r="N7" s="315" t="s">
+      <c r="M7" s="267"/>
+      <c r="N7" s="267" t="s">
         <v>737</v>
       </c>
-      <c r="O7" s="315"/>
+      <c r="O7" s="267"/>
     </row>
     <row r="8" spans="1:15" s="57" customFormat="1" ht="31.5">
-      <c r="A8" s="315"/>
-      <c r="B8" s="315"/>
-      <c r="C8" s="315"/>
-      <c r="D8" s="315"/>
-      <c r="E8" s="315"/>
-      <c r="F8" s="315"/>
-      <c r="G8" s="315"/>
+      <c r="A8" s="267"/>
+      <c r="B8" s="267"/>
+      <c r="C8" s="267"/>
+      <c r="D8" s="267"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="267"/>
       <c r="H8" s="69" t="s">
         <v>325</v>
       </c>
-      <c r="I8" s="315"/>
-      <c r="J8" s="315"/>
-      <c r="K8" s="315"/>
+      <c r="I8" s="267"/>
+      <c r="J8" s="267"/>
+      <c r="K8" s="267"/>
       <c r="L8" s="70" t="s">
         <v>292</v>
       </c>
@@ -23983,14 +23983,14 @@
       </c>
     </row>
     <row r="9" spans="1:15" s="57" customFormat="1" ht="15.75">
-      <c r="A9" s="330" t="s">
+      <c r="A9" s="279" t="s">
         <v>415</v>
       </c>
-      <c r="B9" s="330"/>
-      <c r="C9" s="330"/>
-      <c r="D9" s="330"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
+      <c r="B9" s="279"/>
+      <c r="C9" s="279"/>
+      <c r="D9" s="279"/>
+      <c r="E9" s="279"/>
+      <c r="F9" s="279"/>
       <c r="G9" s="148">
         <f>SUM(G10:G32)</f>
         <v>1</v>
@@ -24017,10 +24017,10 @@
       </c>
     </row>
     <row r="10" spans="1:15" s="57" customFormat="1" ht="38.25">
-      <c r="A10" s="335" t="s">
+      <c r="A10" s="298" t="s">
         <v>290</v>
       </c>
-      <c r="B10" s="302" t="s">
+      <c r="B10" s="282" t="s">
         <v>332</v>
       </c>
       <c r="C10" s="98" t="s">
@@ -24029,13 +24029,13 @@
       <c r="D10" s="103" t="s">
         <v>459</v>
       </c>
-      <c r="E10" s="333" t="s">
+      <c r="E10" s="296" t="s">
         <v>396</v>
       </c>
       <c r="F10" s="103" t="s">
         <v>334</v>
       </c>
-      <c r="G10" s="339">
+      <c r="G10" s="302">
         <v>0.15</v>
       </c>
       <c r="H10" s="83"/>
@@ -24051,32 +24051,32 @@
       <c r="L10" s="78">
         <v>0</v>
       </c>
-      <c r="M10" s="342">
+      <c r="M10" s="305">
         <f>IF(SUM(L12:L15)&gt;=1,$G$10,0)</f>
         <v>0</v>
       </c>
       <c r="N10" s="78">
         <v>0</v>
       </c>
-      <c r="O10" s="342">
+      <c r="O10" s="305">
         <f>IF(SUM(N12:N15)&gt;=1,$G$10,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="57" customFormat="1" ht="25.5">
-      <c r="A11" s="336"/>
-      <c r="B11" s="302"/>
+      <c r="A11" s="299"/>
+      <c r="B11" s="282"/>
       <c r="C11" s="97" t="s">
         <v>486</v>
       </c>
       <c r="D11" s="103" t="s">
         <v>458</v>
       </c>
-      <c r="E11" s="338"/>
+      <c r="E11" s="301"/>
       <c r="F11" s="77" t="s">
         <v>476</v>
       </c>
-      <c r="G11" s="340"/>
+      <c r="G11" s="303"/>
       <c r="H11" s="83"/>
       <c r="I11" s="87" t="s">
         <v>335</v>
@@ -24090,26 +24090,26 @@
       <c r="L11" s="78">
         <v>0</v>
       </c>
-      <c r="M11" s="343"/>
+      <c r="M11" s="306"/>
       <c r="N11" s="78">
         <v>0</v>
       </c>
-      <c r="O11" s="343"/>
+      <c r="O11" s="306"/>
     </row>
     <row r="12" spans="1:15" s="58" customFormat="1" ht="25.5">
-      <c r="A12" s="336"/>
-      <c r="B12" s="302"/>
+      <c r="A12" s="299"/>
+      <c r="B12" s="282"/>
       <c r="C12" s="103" t="s">
         <v>333</v>
       </c>
       <c r="D12" s="103" t="s">
         <v>276</v>
       </c>
-      <c r="E12" s="338"/>
+      <c r="E12" s="301"/>
       <c r="F12" s="103" t="s">
         <v>334</v>
       </c>
-      <c r="G12" s="340"/>
+      <c r="G12" s="303"/>
       <c r="H12" s="62"/>
       <c r="I12" s="87" t="s">
         <v>335</v>
@@ -24123,26 +24123,26 @@
       <c r="L12" s="78">
         <v>0</v>
       </c>
-      <c r="M12" s="343"/>
+      <c r="M12" s="306"/>
       <c r="N12" s="78">
         <v>0</v>
       </c>
-      <c r="O12" s="343"/>
+      <c r="O12" s="306"/>
     </row>
     <row r="13" spans="1:15" s="58" customFormat="1" ht="15.75">
-      <c r="A13" s="336"/>
-      <c r="B13" s="302"/>
-      <c r="C13" s="313" t="s">
+      <c r="A13" s="299"/>
+      <c r="B13" s="282"/>
+      <c r="C13" s="289" t="s">
         <v>340</v>
       </c>
       <c r="D13" s="103" t="s">
         <v>277</v>
       </c>
-      <c r="E13" s="338"/>
+      <c r="E13" s="301"/>
       <c r="F13" s="103" t="s">
         <v>341</v>
       </c>
-      <c r="G13" s="340"/>
+      <c r="G13" s="303"/>
       <c r="H13" s="105"/>
       <c r="I13" s="87" t="s">
         <v>335</v>
@@ -24156,24 +24156,24 @@
       <c r="L13" s="96">
         <v>0</v>
       </c>
-      <c r="M13" s="343"/>
+      <c r="M13" s="306"/>
       <c r="N13" s="96">
         <v>0</v>
       </c>
-      <c r="O13" s="343"/>
+      <c r="O13" s="306"/>
     </row>
     <row r="14" spans="1:15" s="58" customFormat="1" ht="25.5">
-      <c r="A14" s="336"/>
-      <c r="B14" s="302"/>
-      <c r="C14" s="313"/>
+      <c r="A14" s="299"/>
+      <c r="B14" s="282"/>
+      <c r="C14" s="289"/>
       <c r="D14" s="103" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="338"/>
+      <c r="E14" s="301"/>
       <c r="F14" s="103" t="s">
         <v>342</v>
       </c>
-      <c r="G14" s="340"/>
+      <c r="G14" s="303"/>
       <c r="H14" s="105"/>
       <c r="I14" s="87" t="s">
         <v>335</v>
@@ -24187,15 +24187,15 @@
       <c r="L14" s="96">
         <v>0</v>
       </c>
-      <c r="M14" s="343"/>
+      <c r="M14" s="306"/>
       <c r="N14" s="96">
         <v>0</v>
       </c>
-      <c r="O14" s="343"/>
+      <c r="O14" s="306"/>
     </row>
     <row r="15" spans="1:15" s="58" customFormat="1" ht="25.5">
-      <c r="A15" s="336"/>
-      <c r="B15" s="333" t="s">
+      <c r="A15" s="299"/>
+      <c r="B15" s="296" t="s">
         <v>343</v>
       </c>
       <c r="C15" s="97" t="s">
@@ -24204,11 +24204,11 @@
       <c r="D15" s="103" t="s">
         <v>280</v>
       </c>
-      <c r="E15" s="338"/>
+      <c r="E15" s="301"/>
       <c r="F15" s="77" t="s">
         <v>411</v>
       </c>
-      <c r="G15" s="340"/>
+      <c r="G15" s="303"/>
       <c r="H15" s="66"/>
       <c r="I15" s="87" t="s">
         <v>335</v>
@@ -24222,26 +24222,26 @@
       <c r="L15" s="96">
         <v>0</v>
       </c>
-      <c r="M15" s="343"/>
+      <c r="M15" s="306"/>
       <c r="N15" s="96">
         <v>0</v>
       </c>
-      <c r="O15" s="343"/>
+      <c r="O15" s="306"/>
     </row>
     <row r="16" spans="1:15" s="58" customFormat="1" ht="15.75">
-      <c r="A16" s="337"/>
-      <c r="B16" s="334"/>
+      <c r="A16" s="300"/>
+      <c r="B16" s="297"/>
       <c r="C16" s="97" t="s">
         <v>460</v>
       </c>
       <c r="D16" s="77" t="s">
         <v>461</v>
       </c>
-      <c r="E16" s="334"/>
+      <c r="E16" s="297"/>
       <c r="F16" s="77" t="s">
         <v>477</v>
       </c>
-      <c r="G16" s="341"/>
+      <c r="G16" s="304"/>
       <c r="H16" s="66"/>
       <c r="I16" s="87" t="s">
         <v>335</v>
@@ -24255,14 +24255,14 @@
       <c r="L16" s="96">
         <v>0</v>
       </c>
-      <c r="M16" s="344"/>
+      <c r="M16" s="307"/>
       <c r="N16" s="96">
         <v>0</v>
       </c>
-      <c r="O16" s="344"/>
+      <c r="O16" s="307"/>
     </row>
     <row r="17" spans="1:16" s="59" customFormat="1" ht="51">
-      <c r="A17" s="305" t="s">
+      <c r="A17" s="285" t="s">
         <v>281</v>
       </c>
       <c r="B17" s="113" t="s">
@@ -24274,13 +24274,13 @@
       <c r="D17" s="113" t="s">
         <v>316</v>
       </c>
-      <c r="E17" s="308" t="s">
+      <c r="E17" s="286" t="s">
         <v>397</v>
       </c>
       <c r="F17" s="113" t="s">
         <v>404</v>
       </c>
-      <c r="G17" s="310">
+      <c r="G17" s="288">
         <v>0.2</v>
       </c>
       <c r="H17" s="107"/>
@@ -24296,20 +24296,20 @@
       <c r="L17" s="95">
         <v>0</v>
       </c>
-      <c r="M17" s="331">
+      <c r="M17" s="295">
         <f>IF(SUM(L17:L18)&gt;=1,$G$17,0)</f>
         <v>0</v>
       </c>
       <c r="N17" s="95">
         <v>0</v>
       </c>
-      <c r="O17" s="331">
+      <c r="O17" s="295">
         <f>IF(SUM(N17:N18)&gt;=1,$G$17,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="58" customFormat="1" ht="51">
-      <c r="A18" s="305"/>
+      <c r="A18" s="285"/>
       <c r="B18" s="113" t="s">
         <v>407</v>
       </c>
@@ -24319,11 +24319,11 @@
       <c r="D18" s="113" t="s">
         <v>409</v>
       </c>
-      <c r="E18" s="308"/>
+      <c r="E18" s="286"/>
       <c r="F18" s="113" t="s">
         <v>410</v>
       </c>
-      <c r="G18" s="310"/>
+      <c r="G18" s="288"/>
       <c r="H18" s="107"/>
       <c r="I18" s="88" t="s">
         <v>348</v>
@@ -24337,17 +24337,17 @@
       <c r="L18" s="95">
         <v>0</v>
       </c>
-      <c r="M18" s="331"/>
+      <c r="M18" s="295"/>
       <c r="N18" s="95">
         <v>0</v>
       </c>
-      <c r="O18" s="331"/>
+      <c r="O18" s="295"/>
     </row>
     <row r="19" spans="1:16" s="58" customFormat="1" ht="15.75">
-      <c r="A19" s="301" t="s">
+      <c r="A19" s="281" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="313" t="s">
+      <c r="B19" s="289" t="s">
         <v>351</v>
       </c>
       <c r="C19" s="103" t="s">
@@ -24356,13 +24356,13 @@
       <c r="D19" s="103" t="s">
         <v>286</v>
       </c>
-      <c r="E19" s="303" t="s">
+      <c r="E19" s="283" t="s">
         <v>398</v>
       </c>
       <c r="F19" s="103" t="s">
         <v>353</v>
       </c>
-      <c r="G19" s="304">
+      <c r="G19" s="280">
         <v>0.15</v>
       </c>
       <c r="H19" s="105"/>
@@ -24378,32 +24378,32 @@
       <c r="L19" s="96">
         <v>0</v>
       </c>
-      <c r="M19" s="332">
+      <c r="M19" s="308">
         <f>IF(SUM(L19:L21)&gt;=1,$G$19,0)</f>
         <v>0</v>
       </c>
       <c r="N19" s="96">
         <v>0</v>
       </c>
-      <c r="O19" s="332">
+      <c r="O19" s="308">
         <f>IF(SUM(N19:N21)&gt;=1,$G$19,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="58" customFormat="1" ht="38.25">
-      <c r="A20" s="301"/>
-      <c r="B20" s="313"/>
-      <c r="C20" s="314" t="s">
+      <c r="A20" s="281"/>
+      <c r="B20" s="289"/>
+      <c r="C20" s="290" t="s">
         <v>356</v>
       </c>
       <c r="D20" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="E20" s="302"/>
+      <c r="E20" s="282"/>
       <c r="F20" s="103" t="s">
         <v>358</v>
       </c>
-      <c r="G20" s="304"/>
+      <c r="G20" s="280"/>
       <c r="H20" s="105"/>
       <c r="I20" s="105" t="s">
         <v>359</v>
@@ -24417,24 +24417,24 @@
       <c r="L20" s="96">
         <v>0</v>
       </c>
-      <c r="M20" s="332"/>
+      <c r="M20" s="308"/>
       <c r="N20" s="96">
         <v>0</v>
       </c>
-      <c r="O20" s="332"/>
+      <c r="O20" s="308"/>
     </row>
     <row r="21" spans="1:16" s="58" customFormat="1" ht="15.75">
-      <c r="A21" s="301"/>
-      <c r="B21" s="313"/>
-      <c r="C21" s="314"/>
+      <c r="A21" s="281"/>
+      <c r="B21" s="289"/>
+      <c r="C21" s="290"/>
       <c r="D21" s="103" t="s">
         <v>287</v>
       </c>
-      <c r="E21" s="302"/>
+      <c r="E21" s="282"/>
       <c r="F21" s="103" t="s">
         <v>364</v>
       </c>
-      <c r="G21" s="304"/>
+      <c r="G21" s="280"/>
       <c r="H21" s="105"/>
       <c r="I21" s="105">
         <v>0</v>
@@ -24448,32 +24448,32 @@
       <c r="L21" s="96">
         <v>0</v>
       </c>
-      <c r="M21" s="332"/>
+      <c r="M21" s="308"/>
       <c r="N21" s="96">
         <v>0</v>
       </c>
-      <c r="O21" s="332"/>
+      <c r="O21" s="308"/>
     </row>
     <row r="22" spans="1:16" s="58" customFormat="1" ht="25.5">
-      <c r="A22" s="305" t="s">
+      <c r="A22" s="285" t="s">
         <v>282</v>
       </c>
-      <c r="B22" s="309" t="s">
+      <c r="B22" s="287" t="s">
         <v>365</v>
       </c>
-      <c r="C22" s="306" t="s">
+      <c r="C22" s="292" t="s">
         <v>366</v>
       </c>
       <c r="D22" s="113" t="s">
         <v>406</v>
       </c>
-      <c r="E22" s="308" t="s">
+      <c r="E22" s="286" t="s">
         <v>399</v>
       </c>
       <c r="F22" s="108" t="s">
         <v>367</v>
       </c>
-      <c r="G22" s="310">
+      <c r="G22" s="288">
         <v>0.15</v>
       </c>
       <c r="H22" s="107"/>
@@ -24489,30 +24489,30 @@
       <c r="L22" s="95">
         <v>0</v>
       </c>
-      <c r="M22" s="331">
+      <c r="M22" s="295">
         <f>IF(SUM(L22:L23)&gt;=1,$G$22,0)</f>
         <v>0</v>
       </c>
       <c r="N22" s="95">
         <v>0</v>
       </c>
-      <c r="O22" s="331">
+      <c r="O22" s="295">
         <f>IF(SUM(N22:N23)&gt;=1,$G$22,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="58" customFormat="1" ht="25.5">
-      <c r="A23" s="305"/>
-      <c r="B23" s="309"/>
-      <c r="C23" s="306"/>
+      <c r="A23" s="285"/>
+      <c r="B23" s="287"/>
+      <c r="C23" s="292"/>
       <c r="D23" s="113" t="s">
         <v>288</v>
       </c>
-      <c r="E23" s="309"/>
+      <c r="E23" s="287"/>
       <c r="F23" s="108" t="s">
         <v>369</v>
       </c>
-      <c r="G23" s="310"/>
+      <c r="G23" s="288"/>
       <c r="H23" s="107"/>
       <c r="I23" s="107" t="s">
         <v>368</v>
@@ -24526,32 +24526,32 @@
       <c r="L23" s="95">
         <v>0</v>
       </c>
-      <c r="M23" s="331"/>
+      <c r="M23" s="295"/>
       <c r="N23" s="95">
         <v>0</v>
       </c>
-      <c r="O23" s="331"/>
+      <c r="O23" s="295"/>
     </row>
     <row r="24" spans="1:16" ht="25.5">
-      <c r="A24" s="301" t="s">
+      <c r="A24" s="281" t="s">
         <v>283</v>
       </c>
-      <c r="B24" s="302" t="s">
+      <c r="B24" s="282" t="s">
         <v>370</v>
       </c>
-      <c r="C24" s="302" t="s">
+      <c r="C24" s="282" t="s">
         <v>371</v>
       </c>
       <c r="D24" s="77" t="s">
         <v>413</v>
       </c>
-      <c r="E24" s="303" t="s">
+      <c r="E24" s="283" t="s">
         <v>400</v>
       </c>
       <c r="F24" s="77" t="s">
         <v>417</v>
       </c>
-      <c r="G24" s="304">
+      <c r="G24" s="280">
         <v>0.15</v>
       </c>
       <c r="H24" s="105"/>
@@ -24567,30 +24567,30 @@
       <c r="L24" s="96">
         <v>0</v>
       </c>
-      <c r="M24" s="342">
+      <c r="M24" s="305">
         <f>IF(SUM(L24:L26)&gt;=1,$G$24,0)</f>
         <v>0</v>
       </c>
       <c r="N24" s="96">
         <v>0</v>
       </c>
-      <c r="O24" s="342">
+      <c r="O24" s="305">
         <f>IF(SUM(N24:N26)&gt;=1,$G$24,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="25.5">
-      <c r="A25" s="301"/>
-      <c r="B25" s="302"/>
-      <c r="C25" s="302"/>
+      <c r="A25" s="281"/>
+      <c r="B25" s="282"/>
+      <c r="C25" s="282"/>
       <c r="D25" s="103" t="s">
         <v>374</v>
       </c>
-      <c r="E25" s="303"/>
+      <c r="E25" s="283"/>
       <c r="F25" s="103" t="s">
         <v>375</v>
       </c>
-      <c r="G25" s="304"/>
+      <c r="G25" s="280"/>
       <c r="H25" s="105"/>
       <c r="I25" s="71">
         <v>0.01</v>
@@ -24604,24 +24604,24 @@
       <c r="L25" s="96">
         <v>0</v>
       </c>
-      <c r="M25" s="343"/>
+      <c r="M25" s="306"/>
       <c r="N25" s="96">
         <v>0</v>
       </c>
-      <c r="O25" s="343"/>
+      <c r="O25" s="306"/>
     </row>
     <row r="26" spans="1:16" ht="25.5">
-      <c r="A26" s="301"/>
-      <c r="B26" s="302"/>
-      <c r="C26" s="302"/>
+      <c r="A26" s="281"/>
+      <c r="B26" s="282"/>
+      <c r="C26" s="282"/>
       <c r="D26" s="103" t="s">
         <v>376</v>
       </c>
-      <c r="E26" s="303"/>
+      <c r="E26" s="283"/>
       <c r="F26" s="103" t="s">
         <v>377</v>
       </c>
-      <c r="G26" s="304"/>
+      <c r="G26" s="280"/>
       <c r="H26" s="105"/>
       <c r="I26" s="105">
         <v>0.01</v>
@@ -24635,24 +24635,24 @@
       <c r="L26" s="96">
         <v>0</v>
       </c>
-      <c r="M26" s="343"/>
+      <c r="M26" s="306"/>
       <c r="N26" s="96">
         <v>0</v>
       </c>
-      <c r="O26" s="343"/>
+      <c r="O26" s="306"/>
     </row>
     <row r="27" spans="1:16" ht="15.75">
-      <c r="A27" s="301"/>
-      <c r="B27" s="302"/>
-      <c r="C27" s="302"/>
+      <c r="A27" s="281"/>
+      <c r="B27" s="282"/>
+      <c r="C27" s="282"/>
       <c r="D27" s="77" t="s">
         <v>482</v>
       </c>
-      <c r="E27" s="303"/>
+      <c r="E27" s="283"/>
       <c r="F27" s="77" t="s">
         <v>483</v>
       </c>
-      <c r="G27" s="304"/>
+      <c r="G27" s="280"/>
       <c r="H27" s="105"/>
       <c r="I27" s="100" t="s">
         <v>481</v>
@@ -24666,24 +24666,24 @@
       <c r="L27" s="96">
         <v>0</v>
       </c>
-      <c r="M27" s="343"/>
+      <c r="M27" s="306"/>
       <c r="N27" s="96">
         <v>0</v>
       </c>
-      <c r="O27" s="343"/>
+      <c r="O27" s="306"/>
     </row>
     <row r="28" spans="1:16" ht="25.5">
-      <c r="A28" s="301"/>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
+      <c r="A28" s="281"/>
+      <c r="B28" s="282"/>
+      <c r="C28" s="282"/>
       <c r="D28" s="77" t="s">
         <v>484</v>
       </c>
-      <c r="E28" s="303"/>
+      <c r="E28" s="283"/>
       <c r="F28" s="103" t="s">
         <v>375</v>
       </c>
-      <c r="G28" s="304"/>
+      <c r="G28" s="280"/>
       <c r="H28" s="105"/>
       <c r="I28" s="71">
         <v>0.01</v>
@@ -24697,32 +24697,32 @@
       <c r="L28" s="96">
         <v>0</v>
       </c>
-      <c r="M28" s="344"/>
+      <c r="M28" s="307"/>
       <c r="N28" s="96">
         <v>0</v>
       </c>
-      <c r="O28" s="344"/>
+      <c r="O28" s="307"/>
     </row>
     <row r="29" spans="1:16" ht="25.5">
-      <c r="A29" s="305" t="s">
+      <c r="A29" s="285" t="s">
         <v>291</v>
       </c>
-      <c r="B29" s="306" t="s">
+      <c r="B29" s="292" t="s">
         <v>378</v>
       </c>
-      <c r="C29" s="307" t="s">
+      <c r="C29" s="291" t="s">
         <v>465</v>
       </c>
       <c r="D29" s="113" t="s">
         <v>466</v>
       </c>
-      <c r="E29" s="308" t="s">
+      <c r="E29" s="286" t="s">
         <v>401</v>
       </c>
       <c r="F29" s="108" t="s">
         <v>381</v>
       </c>
-      <c r="G29" s="310">
+      <c r="G29" s="288">
         <v>0.15</v>
       </c>
       <c r="H29" s="74"/>
@@ -24738,30 +24738,30 @@
       <c r="L29" s="79">
         <v>0</v>
       </c>
-      <c r="M29" s="331">
+      <c r="M29" s="295">
         <f>IF(SUM(L29:L31)&gt;=1,$G$29,0)</f>
         <v>0</v>
       </c>
       <c r="N29" s="79">
         <v>0</v>
       </c>
-      <c r="O29" s="331">
+      <c r="O29" s="295">
         <f>IF(SUM(N29:N31)&gt;=1,$G$29,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="25.5">
-      <c r="A30" s="305"/>
-      <c r="B30" s="306"/>
-      <c r="C30" s="306"/>
+      <c r="A30" s="285"/>
+      <c r="B30" s="292"/>
+      <c r="C30" s="292"/>
       <c r="D30" s="113" t="s">
         <v>467</v>
       </c>
-      <c r="E30" s="309"/>
+      <c r="E30" s="287"/>
       <c r="F30" s="113" t="s">
         <v>385</v>
       </c>
-      <c r="G30" s="310"/>
+      <c r="G30" s="288"/>
       <c r="H30" s="107"/>
       <c r="I30" s="107" t="s">
         <v>382</v>
@@ -24775,14 +24775,14 @@
       <c r="L30" s="79">
         <v>0</v>
       </c>
-      <c r="M30" s="331"/>
+      <c r="M30" s="295"/>
       <c r="N30" s="79">
         <v>0</v>
       </c>
-      <c r="O30" s="331"/>
+      <c r="O30" s="295"/>
     </row>
     <row r="31" spans="1:16" ht="46.5" customHeight="1">
-      <c r="A31" s="305"/>
+      <c r="A31" s="285"/>
       <c r="B31" s="108" t="s">
         <v>386</v>
       </c>
@@ -24792,11 +24792,11 @@
       <c r="D31" s="113" t="s">
         <v>468</v>
       </c>
-      <c r="E31" s="309"/>
+      <c r="E31" s="287"/>
       <c r="F31" s="108" t="s">
         <v>387</v>
       </c>
-      <c r="G31" s="310"/>
+      <c r="G31" s="288"/>
       <c r="H31" s="107"/>
       <c r="I31" s="76" t="s">
         <v>388</v>
@@ -24810,11 +24810,11 @@
       <c r="L31" s="79">
         <v>0</v>
       </c>
-      <c r="M31" s="331"/>
+      <c r="M31" s="295"/>
       <c r="N31" s="79">
         <v>0</v>
       </c>
-      <c r="O31" s="331"/>
+      <c r="O31" s="295"/>
       <c r="P31" s="208"/>
     </row>
     <row r="32" spans="1:16" ht="26.25">
@@ -24869,6 +24869,49 @@
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="M29:M31"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="G24:G28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="M19:M21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="O19:O21"/>
+    <mergeCell ref="A1:B5"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:H2"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="I6:I8"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
     <mergeCell ref="O22:O23"/>
     <mergeCell ref="O29:O31"/>
     <mergeCell ref="B15:B16"/>
@@ -24885,49 +24928,6 @@
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="M17:M18"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="O19:O21"/>
-    <mergeCell ref="A1:B5"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:H2"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="I6:I8"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="M19:M21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="M29:M31"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="E24:E28"/>
-    <mergeCell ref="G24:G28"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="G29:G31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="63" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -24956,54 +24956,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="319"/>
-      <c r="B1" s="319"/>
-      <c r="C1" s="322" t="s">
+      <c r="A1" s="268"/>
+      <c r="B1" s="268"/>
+      <c r="C1" s="271" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="324" t="str">
+      <c r="D1" s="273" t="str">
         <f>'P3.1.2 (Staff)'!D1:H2</f>
         <v>CÔNG TY TNHH KỸ THUẬT TỰ ĐỘNG AN DƯƠNG
 BẢNG KPI NHÂN VIÊN THÁNG 6 NĂM 2024</v>
       </c>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325"/>
-      <c r="G1" s="325"/>
-      <c r="H1" s="326"/>
+      <c r="E1" s="274"/>
+      <c r="F1" s="274"/>
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
     </row>
     <row r="2" spans="1:13" ht="47.25" customHeight="1">
-      <c r="A2" s="320"/>
-      <c r="B2" s="320"/>
-      <c r="C2" s="323"/>
-      <c r="D2" s="327"/>
-      <c r="E2" s="328"/>
-      <c r="F2" s="328"/>
-      <c r="G2" s="328"/>
-      <c r="H2" s="329"/>
+      <c r="A2" s="269"/>
+      <c r="B2" s="269"/>
+      <c r="C2" s="272"/>
+      <c r="D2" s="276"/>
+      <c r="E2" s="277"/>
+      <c r="F2" s="277"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="320"/>
-      <c r="B3" s="320"/>
+      <c r="A3" s="269"/>
+      <c r="B3" s="269"/>
       <c r="C3" s="53" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="320"/>
-      <c r="B4" s="320"/>
+      <c r="A4" s="269"/>
+      <c r="B4" s="269"/>
       <c r="C4" s="55" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75">
-      <c r="A5" s="321"/>
-      <c r="B5" s="321"/>
+      <c r="A5" s="270"/>
+      <c r="B5" s="270"/>
       <c r="C5" s="144"/>
       <c r="D5" s="145"/>
       <c r="E5" s="145"/>
@@ -25017,73 +25017,73 @@
       <c r="M5" s="145"/>
     </row>
     <row r="6" spans="1:13" ht="15.75">
-      <c r="A6" s="315" t="s">
+      <c r="A6" s="267" t="s">
         <v>405</v>
       </c>
-      <c r="B6" s="315" t="s">
+      <c r="B6" s="267" t="s">
         <v>321</v>
       </c>
-      <c r="C6" s="315" t="s">
+      <c r="C6" s="267" t="s">
         <v>322</v>
       </c>
-      <c r="D6" s="315" t="s">
+      <c r="D6" s="267" t="s">
         <v>289</v>
       </c>
-      <c r="E6" s="315" t="s">
+      <c r="E6" s="267" t="s">
         <v>323</v>
       </c>
-      <c r="F6" s="315" t="s">
+      <c r="F6" s="267" t="s">
         <v>324</v>
       </c>
-      <c r="G6" s="315" t="s">
+      <c r="G6" s="267" t="s">
         <v>416</v>
       </c>
       <c r="H6" s="147"/>
-      <c r="I6" s="315" t="s">
+      <c r="I6" s="267" t="s">
         <v>326</v>
       </c>
-      <c r="J6" s="315" t="s">
+      <c r="J6" s="267" t="s">
         <v>327</v>
       </c>
-      <c r="K6" s="315" t="s">
+      <c r="K6" s="267" t="s">
         <v>328</v>
       </c>
-      <c r="L6" s="315" t="s">
+      <c r="L6" s="267" t="s">
         <v>414</v>
       </c>
-      <c r="M6" s="315"/>
+      <c r="M6" s="267"/>
     </row>
     <row r="7" spans="1:13" ht="15.75">
-      <c r="A7" s="315"/>
-      <c r="B7" s="315"/>
-      <c r="C7" s="315"/>
-      <c r="D7" s="315"/>
-      <c r="E7" s="315"/>
-      <c r="F7" s="315"/>
-      <c r="G7" s="315"/>
+      <c r="A7" s="267"/>
+      <c r="B7" s="267"/>
+      <c r="C7" s="267"/>
+      <c r="D7" s="267"/>
+      <c r="E7" s="267"/>
+      <c r="F7" s="267"/>
+      <c r="G7" s="267"/>
       <c r="H7" s="147"/>
-      <c r="I7" s="315"/>
-      <c r="J7" s="315"/>
-      <c r="K7" s="315"/>
-      <c r="L7" s="315" t="s">
+      <c r="I7" s="267"/>
+      <c r="J7" s="267"/>
+      <c r="K7" s="267"/>
+      <c r="L7" s="267" t="s">
         <v>494</v>
       </c>
-      <c r="M7" s="315"/>
+      <c r="M7" s="267"/>
     </row>
     <row r="8" spans="1:13" s="57" customFormat="1" ht="31.5">
-      <c r="A8" s="315"/>
-      <c r="B8" s="315"/>
-      <c r="C8" s="315"/>
-      <c r="D8" s="315"/>
-      <c r="E8" s="315"/>
-      <c r="F8" s="315"/>
-      <c r="G8" s="315"/>
+      <c r="A8" s="267"/>
+      <c r="B8" s="267"/>
+      <c r="C8" s="267"/>
+      <c r="D8" s="267"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="267"/>
       <c r="H8" s="69" t="s">
         <v>325</v>
       </c>
-      <c r="I8" s="315"/>
-      <c r="J8" s="315"/>
-      <c r="K8" s="315"/>
+      <c r="I8" s="267"/>
+      <c r="J8" s="267"/>
+      <c r="K8" s="267"/>
       <c r="L8" s="70" t="s">
         <v>292</v>
       </c>
@@ -25092,14 +25092,14 @@
       </c>
     </row>
     <row r="9" spans="1:13" s="57" customFormat="1" ht="15.75">
-      <c r="A9" s="330" t="s">
+      <c r="A9" s="279" t="s">
         <v>415</v>
       </c>
-      <c r="B9" s="330"/>
-      <c r="C9" s="330"/>
-      <c r="D9" s="330"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
+      <c r="B9" s="279"/>
+      <c r="C9" s="279"/>
+      <c r="D9" s="279"/>
+      <c r="E9" s="279"/>
+      <c r="F9" s="279"/>
       <c r="G9" s="148">
         <f>SUM(G10:G33)</f>
         <v>1</v>
@@ -25118,10 +25118,10 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="57" customFormat="1" ht="38.25">
-      <c r="A10" s="301" t="s">
+      <c r="A10" s="281" t="s">
         <v>290</v>
       </c>
-      <c r="B10" s="302" t="s">
+      <c r="B10" s="282" t="s">
         <v>332</v>
       </c>
       <c r="C10" s="98" t="s">
@@ -25130,13 +25130,13 @@
       <c r="D10" s="103" t="s">
         <v>459</v>
       </c>
-      <c r="E10" s="303" t="s">
+      <c r="E10" s="283" t="s">
         <v>396</v>
       </c>
       <c r="F10" s="103" t="s">
         <v>334</v>
       </c>
-      <c r="G10" s="304">
+      <c r="G10" s="280">
         <v>0.15</v>
       </c>
       <c r="H10" s="83"/>
@@ -25152,25 +25152,25 @@
       <c r="L10" s="78">
         <v>0</v>
       </c>
-      <c r="M10" s="312">
+      <c r="M10" s="284">
         <f>IF(SUM(L12:L15)&gt;=1,$G$10,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="57" customFormat="1" ht="25.5">
-      <c r="A11" s="301"/>
-      <c r="B11" s="302"/>
+      <c r="A11" s="281"/>
+      <c r="B11" s="282"/>
       <c r="C11" s="97" t="s">
         <v>486</v>
       </c>
       <c r="D11" s="103" t="s">
         <v>458</v>
       </c>
-      <c r="E11" s="303"/>
+      <c r="E11" s="283"/>
       <c r="F11" s="77" t="s">
         <v>476</v>
       </c>
-      <c r="G11" s="304"/>
+      <c r="G11" s="280"/>
       <c r="H11" s="83"/>
       <c r="I11" s="87" t="s">
         <v>335</v>
@@ -25184,22 +25184,22 @@
       <c r="L11" s="78">
         <v>0</v>
       </c>
-      <c r="M11" s="312"/>
+      <c r="M11" s="284"/>
     </row>
     <row r="12" spans="1:13" s="58" customFormat="1" ht="25.5">
-      <c r="A12" s="301"/>
-      <c r="B12" s="302"/>
+      <c r="A12" s="281"/>
+      <c r="B12" s="282"/>
       <c r="C12" s="103" t="s">
         <v>333</v>
       </c>
       <c r="D12" s="103" t="s">
         <v>276</v>
       </c>
-      <c r="E12" s="303"/>
+      <c r="E12" s="283"/>
       <c r="F12" s="103" t="s">
         <v>334</v>
       </c>
-      <c r="G12" s="304"/>
+      <c r="G12" s="280"/>
       <c r="H12" s="62"/>
       <c r="I12" s="87" t="s">
         <v>335</v>
@@ -25213,22 +25213,22 @@
       <c r="L12" s="78">
         <v>0</v>
       </c>
-      <c r="M12" s="312"/>
+      <c r="M12" s="284"/>
     </row>
     <row r="13" spans="1:13" s="58" customFormat="1" ht="15.75">
-      <c r="A13" s="301"/>
-      <c r="B13" s="302"/>
-      <c r="C13" s="313" t="s">
+      <c r="A13" s="281"/>
+      <c r="B13" s="282"/>
+      <c r="C13" s="289" t="s">
         <v>340</v>
       </c>
       <c r="D13" s="103" t="s">
         <v>277</v>
       </c>
-      <c r="E13" s="303"/>
+      <c r="E13" s="283"/>
       <c r="F13" s="103" t="s">
         <v>341</v>
       </c>
-      <c r="G13" s="304"/>
+      <c r="G13" s="280"/>
       <c r="H13" s="105"/>
       <c r="I13" s="87" t="s">
         <v>335</v>
@@ -25242,20 +25242,20 @@
       <c r="L13" s="96">
         <v>0</v>
       </c>
-      <c r="M13" s="312"/>
+      <c r="M13" s="284"/>
     </row>
     <row r="14" spans="1:13" s="58" customFormat="1" ht="25.5">
-      <c r="A14" s="301"/>
-      <c r="B14" s="302"/>
-      <c r="C14" s="313"/>
+      <c r="A14" s="281"/>
+      <c r="B14" s="282"/>
+      <c r="C14" s="289"/>
       <c r="D14" s="103" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="303"/>
+      <c r="E14" s="283"/>
       <c r="F14" s="103" t="s">
         <v>342</v>
       </c>
-      <c r="G14" s="304"/>
+      <c r="G14" s="280"/>
       <c r="H14" s="105"/>
       <c r="I14" s="87" t="s">
         <v>335</v>
@@ -25269,10 +25269,10 @@
       <c r="L14" s="96">
         <v>0</v>
       </c>
-      <c r="M14" s="312"/>
+      <c r="M14" s="284"/>
     </row>
     <row r="15" spans="1:13" s="58" customFormat="1" ht="25.5">
-      <c r="A15" s="301"/>
+      <c r="A15" s="281"/>
       <c r="B15" s="105"/>
       <c r="C15" s="103" t="s">
         <v>346</v>
@@ -25280,11 +25280,11 @@
       <c r="D15" s="103" t="s">
         <v>280</v>
       </c>
-      <c r="E15" s="303"/>
+      <c r="E15" s="283"/>
       <c r="F15" s="77" t="s">
         <v>411</v>
       </c>
-      <c r="G15" s="304"/>
+      <c r="G15" s="280"/>
       <c r="H15" s="66"/>
       <c r="I15" s="87" t="s">
         <v>335</v>
@@ -25298,10 +25298,10 @@
       <c r="L15" s="96">
         <v>0</v>
       </c>
-      <c r="M15" s="312"/>
+      <c r="M15" s="284"/>
     </row>
     <row r="16" spans="1:13" s="59" customFormat="1" ht="51">
-      <c r="A16" s="305" t="s">
+      <c r="A16" s="285" t="s">
         <v>281</v>
       </c>
       <c r="B16" s="113" t="s">
@@ -25313,13 +25313,13 @@
       <c r="D16" s="113" t="s">
         <v>316</v>
       </c>
-      <c r="E16" s="308" t="s">
+      <c r="E16" s="286" t="s">
         <v>397</v>
       </c>
       <c r="F16" s="113" t="s">
         <v>404</v>
       </c>
-      <c r="G16" s="310">
+      <c r="G16" s="288">
         <v>0.2</v>
       </c>
       <c r="H16" s="107"/>
@@ -25335,13 +25335,13 @@
       <c r="L16" s="95">
         <v>0</v>
       </c>
-      <c r="M16" s="312">
+      <c r="M16" s="284">
         <f>IF(SUM(L16:L17)&gt;=1,$G$16,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="58" customFormat="1" ht="51">
-      <c r="A17" s="305"/>
+      <c r="A17" s="285"/>
       <c r="B17" s="113" t="s">
         <v>407</v>
       </c>
@@ -25351,11 +25351,11 @@
       <c r="D17" s="113" t="s">
         <v>409</v>
       </c>
-      <c r="E17" s="308"/>
+      <c r="E17" s="286"/>
       <c r="F17" s="113" t="s">
         <v>410</v>
       </c>
-      <c r="G17" s="310"/>
+      <c r="G17" s="288"/>
       <c r="H17" s="107"/>
       <c r="I17" s="88" t="s">
         <v>348</v>
@@ -25369,10 +25369,10 @@
       <c r="L17" s="95">
         <v>0</v>
       </c>
-      <c r="M17" s="312"/>
+      <c r="M17" s="284"/>
     </row>
     <row r="18" spans="1:13" s="58" customFormat="1" ht="51">
-      <c r="A18" s="305"/>
+      <c r="A18" s="285"/>
       <c r="B18" s="113" t="s">
         <v>488</v>
       </c>
@@ -25401,10 +25401,10 @@
       <c r="M18" s="112"/>
     </row>
     <row r="19" spans="1:13" s="58" customFormat="1" ht="15.75">
-      <c r="A19" s="301" t="s">
+      <c r="A19" s="281" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="313" t="s">
+      <c r="B19" s="289" t="s">
         <v>351</v>
       </c>
       <c r="C19" s="103" t="s">
@@ -25413,13 +25413,13 @@
       <c r="D19" s="103" t="s">
         <v>286</v>
       </c>
-      <c r="E19" s="303" t="s">
+      <c r="E19" s="283" t="s">
         <v>398</v>
       </c>
       <c r="F19" s="103" t="s">
         <v>353</v>
       </c>
-      <c r="G19" s="304">
+      <c r="G19" s="280">
         <v>0.15</v>
       </c>
       <c r="H19" s="105"/>
@@ -25435,25 +25435,25 @@
       <c r="L19" s="96">
         <v>0</v>
       </c>
-      <c r="M19" s="312">
+      <c r="M19" s="284">
         <f>IF(SUM(L19:L22)&gt;=1,$G$19,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="58" customFormat="1" ht="38.25">
-      <c r="A20" s="301"/>
-      <c r="B20" s="313"/>
-      <c r="C20" s="314" t="s">
+      <c r="A20" s="281"/>
+      <c r="B20" s="289"/>
+      <c r="C20" s="290" t="s">
         <v>356</v>
       </c>
       <c r="D20" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="E20" s="302"/>
+      <c r="E20" s="282"/>
       <c r="F20" s="103" t="s">
         <v>358</v>
       </c>
-      <c r="G20" s="304"/>
+      <c r="G20" s="280"/>
       <c r="H20" s="105"/>
       <c r="I20" s="105" t="s">
         <v>359</v>
@@ -25467,20 +25467,20 @@
       <c r="L20" s="96">
         <v>0</v>
       </c>
-      <c r="M20" s="312"/>
+      <c r="M20" s="284"/>
     </row>
     <row r="21" spans="1:13" s="58" customFormat="1" ht="15.75">
-      <c r="A21" s="301"/>
-      <c r="B21" s="313"/>
-      <c r="C21" s="314"/>
+      <c r="A21" s="281"/>
+      <c r="B21" s="289"/>
+      <c r="C21" s="290"/>
       <c r="D21" s="103" t="s">
         <v>361</v>
       </c>
-      <c r="E21" s="302"/>
+      <c r="E21" s="282"/>
       <c r="F21" s="103" t="s">
         <v>362</v>
       </c>
-      <c r="G21" s="304"/>
+      <c r="G21" s="280"/>
       <c r="H21" s="105"/>
       <c r="I21" s="104" t="s">
         <v>363</v>
@@ -25494,20 +25494,20 @@
       <c r="L21" s="96">
         <v>0</v>
       </c>
-      <c r="M21" s="312"/>
+      <c r="M21" s="284"/>
     </row>
     <row r="22" spans="1:13" s="58" customFormat="1" ht="15.75">
-      <c r="A22" s="301"/>
-      <c r="B22" s="313"/>
-      <c r="C22" s="314"/>
+      <c r="A22" s="281"/>
+      <c r="B22" s="289"/>
+      <c r="C22" s="290"/>
       <c r="D22" s="103" t="s">
         <v>287</v>
       </c>
-      <c r="E22" s="302"/>
+      <c r="E22" s="282"/>
       <c r="F22" s="103" t="s">
         <v>364</v>
       </c>
-      <c r="G22" s="304"/>
+      <c r="G22" s="280"/>
       <c r="H22" s="105"/>
       <c r="I22" s="105">
         <v>0</v>
@@ -25521,28 +25521,28 @@
       <c r="L22" s="96">
         <v>0</v>
       </c>
-      <c r="M22" s="312"/>
+      <c r="M22" s="284"/>
     </row>
     <row r="23" spans="1:13" s="58" customFormat="1" ht="25.5">
-      <c r="A23" s="305" t="s">
+      <c r="A23" s="285" t="s">
         <v>282</v>
       </c>
-      <c r="B23" s="309" t="s">
+      <c r="B23" s="287" t="s">
         <v>365</v>
       </c>
-      <c r="C23" s="306" t="s">
+      <c r="C23" s="292" t="s">
         <v>366</v>
       </c>
       <c r="D23" s="113" t="s">
         <v>406</v>
       </c>
-      <c r="E23" s="308" t="s">
+      <c r="E23" s="286" t="s">
         <v>399</v>
       </c>
       <c r="F23" s="108" t="s">
         <v>367</v>
       </c>
-      <c r="G23" s="310">
+      <c r="G23" s="288">
         <v>0.15</v>
       </c>
       <c r="H23" s="107"/>
@@ -25558,23 +25558,23 @@
       <c r="L23" s="95">
         <v>0</v>
       </c>
-      <c r="M23" s="312">
+      <c r="M23" s="284">
         <f>IF(SUM(L23:L24)&gt;=1,$G$23,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="58" customFormat="1" ht="25.5">
-      <c r="A24" s="305"/>
-      <c r="B24" s="309"/>
-      <c r="C24" s="306"/>
+      <c r="A24" s="285"/>
+      <c r="B24" s="287"/>
+      <c r="C24" s="292"/>
       <c r="D24" s="113" t="s">
         <v>288</v>
       </c>
-      <c r="E24" s="309"/>
+      <c r="E24" s="287"/>
       <c r="F24" s="108" t="s">
         <v>369</v>
       </c>
-      <c r="G24" s="310"/>
+      <c r="G24" s="288"/>
       <c r="H24" s="107"/>
       <c r="I24" s="107" t="s">
         <v>368</v>
@@ -25588,28 +25588,28 @@
       <c r="L24" s="95">
         <v>0</v>
       </c>
-      <c r="M24" s="312"/>
+      <c r="M24" s="284"/>
     </row>
     <row r="25" spans="1:13" ht="25.5">
-      <c r="A25" s="301" t="s">
+      <c r="A25" s="281" t="s">
         <v>283</v>
       </c>
-      <c r="B25" s="302" t="s">
+      <c r="B25" s="282" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="302" t="s">
+      <c r="C25" s="282" t="s">
         <v>371</v>
       </c>
       <c r="D25" s="77" t="s">
         <v>413</v>
       </c>
-      <c r="E25" s="303" t="s">
+      <c r="E25" s="283" t="s">
         <v>400</v>
       </c>
       <c r="F25" s="77" t="s">
         <v>417</v>
       </c>
-      <c r="G25" s="304">
+      <c r="G25" s="280">
         <v>0.15</v>
       </c>
       <c r="H25" s="105"/>
@@ -25625,23 +25625,23 @@
       <c r="L25" s="96">
         <v>0</v>
       </c>
-      <c r="M25" s="300">
+      <c r="M25" s="293">
         <f>IF(SUM(L25:L27)&gt;=1,$G$25,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="25.5">
-      <c r="A26" s="301"/>
-      <c r="B26" s="302"/>
-      <c r="C26" s="302"/>
+      <c r="A26" s="281"/>
+      <c r="B26" s="282"/>
+      <c r="C26" s="282"/>
       <c r="D26" s="103" t="s">
         <v>374</v>
       </c>
-      <c r="E26" s="303"/>
+      <c r="E26" s="283"/>
       <c r="F26" s="103" t="s">
         <v>375</v>
       </c>
-      <c r="G26" s="304"/>
+      <c r="G26" s="280"/>
       <c r="H26" s="105"/>
       <c r="I26" s="71">
         <v>0.01</v>
@@ -25655,20 +25655,20 @@
       <c r="L26" s="96">
         <v>0</v>
       </c>
-      <c r="M26" s="300"/>
+      <c r="M26" s="293"/>
     </row>
     <row r="27" spans="1:13" ht="25.5">
-      <c r="A27" s="301"/>
-      <c r="B27" s="302"/>
-      <c r="C27" s="302"/>
+      <c r="A27" s="281"/>
+      <c r="B27" s="282"/>
+      <c r="C27" s="282"/>
       <c r="D27" s="103" t="s">
         <v>376</v>
       </c>
-      <c r="E27" s="303"/>
+      <c r="E27" s="283"/>
       <c r="F27" s="103" t="s">
         <v>377</v>
       </c>
-      <c r="G27" s="304"/>
+      <c r="G27" s="280"/>
       <c r="H27" s="105"/>
       <c r="I27" s="105">
         <v>0.01</v>
@@ -25682,20 +25682,20 @@
       <c r="L27" s="96">
         <v>0</v>
       </c>
-      <c r="M27" s="300"/>
+      <c r="M27" s="293"/>
     </row>
     <row r="28" spans="1:13" ht="15.75">
-      <c r="A28" s="301"/>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
+      <c r="A28" s="281"/>
+      <c r="B28" s="282"/>
+      <c r="C28" s="282"/>
       <c r="D28" s="77" t="s">
         <v>482</v>
       </c>
-      <c r="E28" s="303"/>
+      <c r="E28" s="283"/>
       <c r="F28" s="77" t="s">
         <v>483</v>
       </c>
-      <c r="G28" s="304"/>
+      <c r="G28" s="280"/>
       <c r="H28" s="105"/>
       <c r="I28" s="100" t="s">
         <v>481</v>
@@ -25710,17 +25710,17 @@
       <c r="M28" s="111"/>
     </row>
     <row r="29" spans="1:13" ht="25.5">
-      <c r="A29" s="301"/>
-      <c r="B29" s="302"/>
-      <c r="C29" s="302"/>
+      <c r="A29" s="281"/>
+      <c r="B29" s="282"/>
+      <c r="C29" s="282"/>
       <c r="D29" s="77" t="s">
         <v>484</v>
       </c>
-      <c r="E29" s="303"/>
+      <c r="E29" s="283"/>
       <c r="F29" s="103" t="s">
         <v>375</v>
       </c>
-      <c r="G29" s="304"/>
+      <c r="G29" s="280"/>
       <c r="H29" s="105"/>
       <c r="I29" s="71">
         <v>0.01</v>
@@ -25735,25 +25735,25 @@
       <c r="M29" s="111"/>
     </row>
     <row r="30" spans="1:13" ht="15.75">
-      <c r="A30" s="305" t="s">
+      <c r="A30" s="285" t="s">
         <v>291</v>
       </c>
-      <c r="B30" s="306" t="s">
+      <c r="B30" s="292" t="s">
         <v>378</v>
       </c>
-      <c r="C30" s="306" t="s">
+      <c r="C30" s="292" t="s">
         <v>379</v>
       </c>
       <c r="D30" s="108" t="s">
         <v>380</v>
       </c>
-      <c r="E30" s="308" t="s">
+      <c r="E30" s="286" t="s">
         <v>401</v>
       </c>
       <c r="F30" s="108" t="s">
         <v>381</v>
       </c>
-      <c r="G30" s="310">
+      <c r="G30" s="288">
         <v>0.15</v>
       </c>
       <c r="H30" s="74"/>
@@ -25769,23 +25769,23 @@
       <c r="L30" s="79">
         <v>0</v>
       </c>
-      <c r="M30" s="300">
+      <c r="M30" s="293">
         <f>IF(SUM(L30:L32)&gt;=1,$G$30,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="25.5">
-      <c r="A31" s="305"/>
-      <c r="B31" s="306"/>
-      <c r="C31" s="306"/>
+      <c r="A31" s="285"/>
+      <c r="B31" s="292"/>
+      <c r="C31" s="292"/>
       <c r="D31" s="108" t="s">
         <v>284</v>
       </c>
-      <c r="E31" s="309"/>
+      <c r="E31" s="287"/>
       <c r="F31" s="108" t="s">
         <v>385</v>
       </c>
-      <c r="G31" s="310"/>
+      <c r="G31" s="288"/>
       <c r="H31" s="107"/>
       <c r="I31" s="107" t="s">
         <v>382</v>
@@ -25799,10 +25799,10 @@
       <c r="L31" s="79">
         <v>0</v>
       </c>
-      <c r="M31" s="300"/>
+      <c r="M31" s="293"/>
     </row>
     <row r="32" spans="1:13" ht="25.5">
-      <c r="A32" s="305"/>
+      <c r="A32" s="285"/>
       <c r="B32" s="108" t="s">
         <v>386</v>
       </c>
@@ -25812,11 +25812,11 @@
       <c r="D32" s="108" t="s">
         <v>285</v>
       </c>
-      <c r="E32" s="309"/>
+      <c r="E32" s="287"/>
       <c r="F32" s="108" t="s">
         <v>387</v>
       </c>
-      <c r="G32" s="310"/>
+      <c r="G32" s="288"/>
       <c r="H32" s="107"/>
       <c r="I32" s="76" t="s">
         <v>388</v>
@@ -25830,7 +25830,7 @@
       <c r="L32" s="79">
         <v>0</v>
       </c>
-      <c r="M32" s="300"/>
+      <c r="M32" s="293"/>
     </row>
     <row r="33" spans="1:13" ht="48">
       <c r="A33" s="102" t="s">
@@ -25877,6 +25877,40 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="M30:M32"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="B25:B29"/>
+    <mergeCell ref="C25:C29"/>
+    <mergeCell ref="E25:E29"/>
+    <mergeCell ref="G25:G29"/>
+    <mergeCell ref="M25:M27"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="E19:E22"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="M19:M22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="G10:G15"/>
+    <mergeCell ref="M10:M15"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="A1:B5"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:H2"/>
@@ -25893,40 +25927,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="L7:M7"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="G10:G15"/>
-    <mergeCell ref="M10:M15"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="E19:E22"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="M19:M22"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="M30:M32"/>
-    <mergeCell ref="A25:A29"/>
-    <mergeCell ref="B25:B29"/>
-    <mergeCell ref="C25:C29"/>
-    <mergeCell ref="E25:E29"/>
-    <mergeCell ref="G25:G29"/>
-    <mergeCell ref="M25:M27"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="G30:G32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -25957,46 +25957,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20.25">
-      <c r="A1" s="319"/>
-      <c r="B1" s="319"/>
-      <c r="C1" s="322" t="s">
+      <c r="A1" s="268"/>
+      <c r="B1" s="268"/>
+      <c r="C1" s="271" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="324" t="s">
+      <c r="D1" s="273" t="s">
         <v>745</v>
       </c>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325"/>
-      <c r="G1" s="325"/>
-      <c r="H1" s="326"/>
+      <c r="E1" s="274"/>
+      <c r="F1" s="274"/>
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
       <c r="I1" s="52"/>
       <c r="J1" s="52"/>
       <c r="K1" s="52"/>
-      <c r="L1" s="380" t="s">
+      <c r="L1" s="312" t="s">
         <v>318</v>
       </c>
-      <c r="M1" s="380"/>
-      <c r="N1" s="380"/>
+      <c r="M1" s="312"/>
+      <c r="N1" s="312"/>
     </row>
     <row r="2" spans="1:17" ht="20.25">
-      <c r="A2" s="320"/>
-      <c r="B2" s="320"/>
-      <c r="C2" s="323"/>
-      <c r="D2" s="327"/>
-      <c r="E2" s="328"/>
-      <c r="F2" s="328"/>
-      <c r="G2" s="328"/>
-      <c r="H2" s="329"/>
+      <c r="A2" s="269"/>
+      <c r="B2" s="269"/>
+      <c r="C2" s="272"/>
+      <c r="D2" s="276"/>
+      <c r="E2" s="277"/>
+      <c r="F2" s="277"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278"/>
       <c r="I2" s="52"/>
       <c r="J2" s="52"/>
       <c r="K2" s="52"/>
-      <c r="L2" s="380"/>
-      <c r="M2" s="380"/>
-      <c r="N2" s="380"/>
+      <c r="L2" s="312"/>
+      <c r="M2" s="312"/>
+      <c r="N2" s="312"/>
     </row>
     <row r="3" spans="1:17" ht="15.75">
-      <c r="A3" s="320"/>
-      <c r="B3" s="320"/>
+      <c r="A3" s="269"/>
+      <c r="B3" s="269"/>
       <c r="C3" s="53" t="s">
         <v>319</v>
       </c>
@@ -26006,23 +26006,23 @@
       <c r="G3" s="143" t="s">
         <v>498</v>
       </c>
-      <c r="L3" s="380"/>
-      <c r="M3" s="380"/>
-      <c r="N3" s="380"/>
+      <c r="L3" s="312"/>
+      <c r="M3" s="312"/>
+      <c r="N3" s="312"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="320"/>
-      <c r="B4" s="320"/>
+      <c r="A4" s="269"/>
+      <c r="B4" s="269"/>
       <c r="C4" s="55" t="s">
         <v>320</v>
       </c>
-      <c r="L4" s="380"/>
-      <c r="M4" s="380"/>
-      <c r="N4" s="380"/>
+      <c r="L4" s="312"/>
+      <c r="M4" s="312"/>
+      <c r="N4" s="312"/>
     </row>
     <row r="5" spans="1:17" ht="15.75">
-      <c r="A5" s="321"/>
-      <c r="B5" s="321"/>
+      <c r="A5" s="270"/>
+      <c r="B5" s="270"/>
       <c r="C5" s="144"/>
       <c r="D5" s="145"/>
       <c r="E5" s="145"/>
@@ -26032,86 +26032,86 @@
       <c r="I5" s="146"/>
       <c r="J5" s="146"/>
       <c r="K5" s="146"/>
-      <c r="L5" s="381"/>
-      <c r="M5" s="381"/>
-      <c r="N5" s="381"/>
+      <c r="L5" s="313"/>
+      <c r="M5" s="313"/>
+      <c r="N5" s="313"/>
       <c r="O5" s="145"/>
       <c r="P5" s="145"/>
     </row>
     <row r="6" spans="1:17" ht="20.25">
-      <c r="A6" s="315" t="s">
+      <c r="A6" s="267" t="s">
         <v>405</v>
       </c>
-      <c r="B6" s="315" t="s">
+      <c r="B6" s="267" t="s">
         <v>321</v>
       </c>
-      <c r="C6" s="315" t="s">
+      <c r="C6" s="267" t="s">
         <v>322</v>
       </c>
-      <c r="D6" s="315" t="s">
+      <c r="D6" s="267" t="s">
         <v>289</v>
       </c>
-      <c r="E6" s="315" t="s">
+      <c r="E6" s="267" t="s">
         <v>323</v>
       </c>
-      <c r="F6" s="315" t="s">
+      <c r="F6" s="267" t="s">
         <v>324</v>
       </c>
-      <c r="G6" s="315" t="s">
+      <c r="G6" s="267" t="s">
         <v>416</v>
       </c>
       <c r="H6" s="147"/>
-      <c r="I6" s="315" t="s">
+      <c r="I6" s="267" t="s">
         <v>749</v>
       </c>
-      <c r="J6" s="315" t="s">
+      <c r="J6" s="267" t="s">
         <v>327</v>
       </c>
-      <c r="K6" s="315" t="s">
+      <c r="K6" s="267" t="s">
         <v>328</v>
       </c>
       <c r="L6" s="227"/>
       <c r="M6" s="227"/>
       <c r="N6" s="227"/>
-      <c r="O6" s="315" t="s">
+      <c r="O6" s="267" t="s">
         <v>414</v>
       </c>
-      <c r="P6" s="315"/>
+      <c r="P6" s="267"/>
     </row>
     <row r="7" spans="1:17" ht="20.25">
-      <c r="A7" s="315"/>
-      <c r="B7" s="315"/>
-      <c r="C7" s="315"/>
-      <c r="D7" s="315"/>
-      <c r="E7" s="315"/>
-      <c r="F7" s="315"/>
-      <c r="G7" s="315"/>
+      <c r="A7" s="267"/>
+      <c r="B7" s="267"/>
+      <c r="C7" s="267"/>
+      <c r="D7" s="267"/>
+      <c r="E7" s="267"/>
+      <c r="F7" s="267"/>
+      <c r="G7" s="267"/>
       <c r="H7" s="147"/>
-      <c r="I7" s="315"/>
-      <c r="J7" s="315"/>
-      <c r="K7" s="315"/>
+      <c r="I7" s="267"/>
+      <c r="J7" s="267"/>
+      <c r="K7" s="267"/>
       <c r="L7" s="227"/>
       <c r="M7" s="227"/>
       <c r="N7" s="227"/>
-      <c r="O7" s="315" t="s">
+      <c r="O7" s="267" t="s">
         <v>495</v>
       </c>
-      <c r="P7" s="315"/>
+      <c r="P7" s="267"/>
     </row>
     <row r="8" spans="1:17" s="57" customFormat="1" ht="51.95" customHeight="1">
-      <c r="A8" s="315"/>
-      <c r="B8" s="315"/>
-      <c r="C8" s="315"/>
-      <c r="D8" s="315"/>
-      <c r="E8" s="315"/>
-      <c r="F8" s="315"/>
-      <c r="G8" s="315"/>
+      <c r="A8" s="267"/>
+      <c r="B8" s="267"/>
+      <c r="C8" s="267"/>
+      <c r="D8" s="267"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="267"/>
       <c r="H8" s="69" t="s">
         <v>325</v>
       </c>
-      <c r="I8" s="315"/>
-      <c r="J8" s="315"/>
-      <c r="K8" s="315"/>
+      <c r="I8" s="267"/>
+      <c r="J8" s="267"/>
+      <c r="K8" s="267"/>
       <c r="L8" s="70" t="s">
         <v>329</v>
       </c>
@@ -26129,14 +26129,14 @@
       </c>
     </row>
     <row r="9" spans="1:17" s="57" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A9" s="368" t="s">
+      <c r="A9" s="337" t="s">
         <v>415</v>
       </c>
-      <c r="B9" s="369"/>
-      <c r="C9" s="369"/>
-      <c r="D9" s="369"/>
-      <c r="E9" s="369"/>
-      <c r="F9" s="370"/>
+      <c r="B9" s="338"/>
+      <c r="C9" s="338"/>
+      <c r="D9" s="338"/>
+      <c r="E9" s="338"/>
+      <c r="F9" s="339"/>
       <c r="G9" s="85">
         <f>SUM(G10:G35)</f>
         <v>1</v>
@@ -26158,10 +26158,10 @@
       </c>
     </row>
     <row r="10" spans="1:17" s="57" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A10" s="335" t="s">
+      <c r="A10" s="298" t="s">
         <v>290</v>
       </c>
-      <c r="B10" s="360" t="s">
+      <c r="B10" s="342" t="s">
         <v>332</v>
       </c>
       <c r="C10" s="230" t="s">
@@ -26170,13 +26170,13 @@
       <c r="D10" s="103" t="s">
         <v>459</v>
       </c>
-      <c r="E10" s="373" t="s">
+      <c r="E10" s="314" t="s">
         <v>396</v>
       </c>
       <c r="F10" s="103" t="s">
         <v>334</v>
       </c>
-      <c r="G10" s="339">
+      <c r="G10" s="302">
         <v>0.15</v>
       </c>
       <c r="H10" s="83"/>
@@ -26195,26 +26195,26 @@
       <c r="O10" s="78">
         <v>0</v>
       </c>
-      <c r="P10" s="351">
+      <c r="P10" s="319">
         <f>IF(SUM(O10:O16)&gt;=1,$G$10,0)</f>
         <v>0.15</v>
       </c>
       <c r="Q10" s="204"/>
     </row>
     <row r="11" spans="1:17" s="57" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A11" s="336"/>
-      <c r="B11" s="361"/>
+      <c r="A11" s="299"/>
+      <c r="B11" s="343"/>
       <c r="C11" s="97" t="s">
         <v>486</v>
       </c>
       <c r="D11" s="103" t="s">
         <v>458</v>
       </c>
-      <c r="E11" s="374"/>
+      <c r="E11" s="315"/>
       <c r="F11" s="231" t="s">
         <v>476</v>
       </c>
-      <c r="G11" s="340"/>
+      <c r="G11" s="303"/>
       <c r="H11" s="83"/>
       <c r="I11" s="87" t="s">
         <v>335</v>
@@ -26231,23 +26231,23 @@
       <c r="O11" s="78">
         <v>0</v>
       </c>
-      <c r="P11" s="352"/>
+      <c r="P11" s="320"/>
       <c r="Q11" s="204"/>
     </row>
     <row r="12" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A12" s="336"/>
-      <c r="B12" s="361"/>
+      <c r="A12" s="299"/>
+      <c r="B12" s="343"/>
       <c r="C12" s="103" t="s">
         <v>333</v>
       </c>
       <c r="D12" s="103" t="s">
         <v>276</v>
       </c>
-      <c r="E12" s="374"/>
+      <c r="E12" s="315"/>
       <c r="F12" s="103" t="s">
         <v>334</v>
       </c>
-      <c r="G12" s="340"/>
+      <c r="G12" s="303"/>
       <c r="H12" s="62"/>
       <c r="I12" s="87" t="s">
         <v>335</v>
@@ -26270,23 +26270,23 @@
       <c r="O12" s="78">
         <v>0</v>
       </c>
-      <c r="P12" s="352"/>
+      <c r="P12" s="320"/>
       <c r="Q12" s="205"/>
     </row>
     <row r="13" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A13" s="336"/>
-      <c r="B13" s="361"/>
-      <c r="C13" s="371" t="s">
+      <c r="A13" s="299"/>
+      <c r="B13" s="343"/>
+      <c r="C13" s="322" t="s">
         <v>340</v>
       </c>
       <c r="D13" s="103" t="s">
         <v>277</v>
       </c>
-      <c r="E13" s="374"/>
+      <c r="E13" s="315"/>
       <c r="F13" s="103" t="s">
         <v>341</v>
       </c>
-      <c r="G13" s="340"/>
+      <c r="G13" s="303"/>
       <c r="H13" s="105"/>
       <c r="I13" s="87" t="s">
         <v>335</v>
@@ -26309,21 +26309,21 @@
       <c r="O13" s="96">
         <v>0</v>
       </c>
-      <c r="P13" s="352"/>
+      <c r="P13" s="320"/>
       <c r="Q13" s="205"/>
     </row>
     <row r="14" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A14" s="336"/>
-      <c r="B14" s="362"/>
-      <c r="C14" s="372"/>
+      <c r="A14" s="299"/>
+      <c r="B14" s="344"/>
+      <c r="C14" s="324"/>
       <c r="D14" s="103" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="374"/>
+      <c r="E14" s="315"/>
       <c r="F14" s="103" t="s">
         <v>342</v>
       </c>
-      <c r="G14" s="340"/>
+      <c r="G14" s="303"/>
       <c r="H14" s="105"/>
       <c r="I14" s="87" t="s">
         <v>335</v>
@@ -26340,12 +26340,12 @@
       <c r="O14" s="96">
         <v>0</v>
       </c>
-      <c r="P14" s="352"/>
+      <c r="P14" s="320"/>
       <c r="Q14" s="205"/>
     </row>
     <row r="15" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A15" s="336"/>
-      <c r="B15" s="360" t="s">
+      <c r="A15" s="299"/>
+      <c r="B15" s="342" t="s">
         <v>343</v>
       </c>
       <c r="C15" s="103" t="s">
@@ -26354,11 +26354,11 @@
       <c r="D15" s="103" t="s">
         <v>279</v>
       </c>
-      <c r="E15" s="374"/>
+      <c r="E15" s="315"/>
       <c r="F15" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="G15" s="340"/>
+      <c r="G15" s="303"/>
       <c r="H15" s="105"/>
       <c r="I15" s="87" t="s">
         <v>335</v>
@@ -26381,23 +26381,23 @@
       <c r="O15" s="96">
         <v>1</v>
       </c>
-      <c r="P15" s="352"/>
+      <c r="P15" s="320"/>
       <c r="Q15" s="205"/>
     </row>
     <row r="16" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A16" s="337"/>
-      <c r="B16" s="362"/>
+      <c r="A16" s="300"/>
+      <c r="B16" s="344"/>
       <c r="C16" s="103" t="s">
         <v>346</v>
       </c>
       <c r="D16" s="103" t="s">
         <v>280</v>
       </c>
-      <c r="E16" s="375"/>
+      <c r="E16" s="316"/>
       <c r="F16" s="231" t="s">
         <v>411</v>
       </c>
-      <c r="G16" s="341"/>
+      <c r="G16" s="304"/>
       <c r="H16" s="66"/>
       <c r="I16" s="87" t="s">
         <v>335</v>
@@ -26420,11 +26420,11 @@
       <c r="O16" s="96">
         <v>0</v>
       </c>
-      <c r="P16" s="353"/>
+      <c r="P16" s="321"/>
       <c r="Q16" s="205"/>
     </row>
     <row r="17" spans="1:17" s="59" customFormat="1" ht="53.1" customHeight="1">
-      <c r="A17" s="354" t="s">
+      <c r="A17" s="329" t="s">
         <v>281</v>
       </c>
       <c r="B17" s="203" t="s">
@@ -26436,13 +26436,13 @@
       <c r="D17" s="203" t="s">
         <v>316</v>
       </c>
-      <c r="E17" s="357" t="s">
+      <c r="E17" s="335" t="s">
         <v>397</v>
       </c>
       <c r="F17" s="203" t="s">
         <v>404</v>
       </c>
-      <c r="G17" s="345">
+      <c r="G17" s="317">
         <v>0.2</v>
       </c>
       <c r="H17" s="107"/>
@@ -26467,14 +26467,14 @@
       <c r="O17" s="95">
         <v>0</v>
       </c>
-      <c r="P17" s="348">
+      <c r="P17" s="309">
         <f>IF(SUM(O17:O19)&gt;=1,$G$17,0)</f>
         <v>0</v>
       </c>
       <c r="Q17" s="205"/>
     </row>
     <row r="18" spans="1:17" s="58" customFormat="1" ht="51">
-      <c r="A18" s="355"/>
+      <c r="A18" s="340"/>
       <c r="B18" s="203" t="s">
         <v>407</v>
       </c>
@@ -26484,11 +26484,11 @@
       <c r="D18" s="203" t="s">
         <v>409</v>
       </c>
-      <c r="E18" s="358"/>
+      <c r="E18" s="341"/>
       <c r="F18" s="203" t="s">
         <v>410</v>
       </c>
-      <c r="G18" s="346"/>
+      <c r="G18" s="328"/>
       <c r="H18" s="107"/>
       <c r="I18" s="88" t="s">
         <v>348</v>
@@ -26511,11 +26511,11 @@
       <c r="O18" s="95">
         <v>0</v>
       </c>
-      <c r="P18" s="349"/>
+      <c r="P18" s="310"/>
       <c r="Q18" s="205"/>
     </row>
     <row r="19" spans="1:17" s="58" customFormat="1" ht="51">
-      <c r="A19" s="356"/>
+      <c r="A19" s="330"/>
       <c r="B19" s="203" t="s">
         <v>488</v>
       </c>
@@ -26525,11 +26525,11 @@
       <c r="D19" s="203" t="s">
         <v>490</v>
       </c>
-      <c r="E19" s="359"/>
+      <c r="E19" s="336"/>
       <c r="F19" s="203" t="s">
         <v>491</v>
       </c>
-      <c r="G19" s="347"/>
+      <c r="G19" s="318"/>
       <c r="H19" s="107"/>
       <c r="I19" s="88" t="s">
         <v>348</v>
@@ -26546,14 +26546,14 @@
       <c r="O19" s="95">
         <v>0</v>
       </c>
-      <c r="P19" s="350"/>
+      <c r="P19" s="311"/>
       <c r="Q19" s="205"/>
     </row>
     <row r="20" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A20" s="335" t="s">
+      <c r="A20" s="298" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="371" t="s">
+      <c r="B20" s="322" t="s">
         <v>351</v>
       </c>
       <c r="C20" s="103" t="s">
@@ -26562,13 +26562,13 @@
       <c r="D20" s="103" t="s">
         <v>286</v>
       </c>
-      <c r="E20" s="373" t="s">
+      <c r="E20" s="314" t="s">
         <v>398</v>
       </c>
       <c r="F20" s="103" t="s">
         <v>353</v>
       </c>
-      <c r="G20" s="339">
+      <c r="G20" s="302">
         <v>0.15</v>
       </c>
       <c r="H20" s="105"/>
@@ -26593,26 +26593,26 @@
       <c r="O20" s="96">
         <v>0</v>
       </c>
-      <c r="P20" s="351">
+      <c r="P20" s="319">
         <f>IF(SUM(O20:O23)&gt;=1,$G$20,0)</f>
         <v>0</v>
       </c>
       <c r="Q20" s="205"/>
     </row>
     <row r="21" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A21" s="336"/>
-      <c r="B21" s="376"/>
-      <c r="C21" s="377" t="s">
+      <c r="A21" s="299"/>
+      <c r="B21" s="323"/>
+      <c r="C21" s="325" t="s">
         <v>356</v>
       </c>
       <c r="D21" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="E21" s="374"/>
+      <c r="E21" s="315"/>
       <c r="F21" s="103" t="s">
         <v>358</v>
       </c>
-      <c r="G21" s="340"/>
+      <c r="G21" s="303"/>
       <c r="H21" s="105"/>
       <c r="I21" s="105" t="s">
         <v>359</v>
@@ -26635,21 +26635,21 @@
       <c r="O21" s="96">
         <v>0</v>
       </c>
-      <c r="P21" s="352"/>
+      <c r="P21" s="320"/>
       <c r="Q21" s="205"/>
     </row>
     <row r="22" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A22" s="336"/>
-      <c r="B22" s="376"/>
-      <c r="C22" s="378"/>
+      <c r="A22" s="299"/>
+      <c r="B22" s="323"/>
+      <c r="C22" s="326"/>
       <c r="D22" s="103" t="s">
         <v>361</v>
       </c>
-      <c r="E22" s="374"/>
+      <c r="E22" s="315"/>
       <c r="F22" s="103" t="s">
         <v>362</v>
       </c>
-      <c r="G22" s="340"/>
+      <c r="G22" s="303"/>
       <c r="H22" s="105"/>
       <c r="I22" s="232" t="s">
         <v>363</v>
@@ -26666,21 +26666,21 @@
       <c r="O22" s="96">
         <v>0</v>
       </c>
-      <c r="P22" s="352"/>
+      <c r="P22" s="320"/>
       <c r="Q22" s="206"/>
     </row>
     <row r="23" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A23" s="337"/>
-      <c r="B23" s="372"/>
-      <c r="C23" s="379"/>
+      <c r="A23" s="300"/>
+      <c r="B23" s="324"/>
+      <c r="C23" s="327"/>
       <c r="D23" s="103" t="s">
         <v>287</v>
       </c>
-      <c r="E23" s="375"/>
+      <c r="E23" s="316"/>
       <c r="F23" s="103" t="s">
         <v>364</v>
       </c>
-      <c r="G23" s="341"/>
+      <c r="G23" s="304"/>
       <c r="H23" s="105"/>
       <c r="I23" s="105">
         <v>0</v>
@@ -26703,29 +26703,29 @@
       <c r="O23" s="96">
         <v>0</v>
       </c>
-      <c r="P23" s="353"/>
+      <c r="P23" s="321"/>
       <c r="Q23" s="205"/>
     </row>
     <row r="24" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A24" s="354" t="s">
+      <c r="A24" s="329" t="s">
         <v>282</v>
       </c>
-      <c r="B24" s="363" t="s">
+      <c r="B24" s="331" t="s">
         <v>365</v>
       </c>
-      <c r="C24" s="366" t="s">
+      <c r="C24" s="333" t="s">
         <v>366</v>
       </c>
       <c r="D24" s="203" t="s">
         <v>406</v>
       </c>
-      <c r="E24" s="357" t="s">
+      <c r="E24" s="335" t="s">
         <v>399</v>
       </c>
       <c r="F24" s="108" t="s">
         <v>367</v>
       </c>
-      <c r="G24" s="345">
+      <c r="G24" s="317">
         <v>0.15</v>
       </c>
       <c r="H24" s="107"/>
@@ -26750,24 +26750,24 @@
       <c r="O24" s="95">
         <v>0</v>
       </c>
-      <c r="P24" s="348">
+      <c r="P24" s="309">
         <f>IF(SUM(O24:O25)&gt;=1,$G$24,0)</f>
         <v>0</v>
       </c>
       <c r="Q24" s="205"/>
     </row>
     <row r="25" spans="1:17" s="58" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A25" s="356"/>
-      <c r="B25" s="365"/>
-      <c r="C25" s="367"/>
+      <c r="A25" s="330"/>
+      <c r="B25" s="332"/>
+      <c r="C25" s="334"/>
       <c r="D25" s="203" t="s">
         <v>288</v>
       </c>
-      <c r="E25" s="359"/>
+      <c r="E25" s="336"/>
       <c r="F25" s="108" t="s">
         <v>369</v>
       </c>
-      <c r="G25" s="347"/>
+      <c r="G25" s="318"/>
       <c r="H25" s="107"/>
       <c r="I25" s="107" t="s">
         <v>368</v>
@@ -26784,29 +26784,29 @@
       <c r="O25" s="95">
         <v>0</v>
       </c>
-      <c r="P25" s="350"/>
+      <c r="P25" s="311"/>
       <c r="Q25" s="205"/>
     </row>
     <row r="26" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A26" s="335" t="s">
+      <c r="A26" s="298" t="s">
         <v>283</v>
       </c>
-      <c r="B26" s="360" t="s">
+      <c r="B26" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C26" s="360" t="s">
+      <c r="C26" s="342" t="s">
         <v>371</v>
       </c>
       <c r="D26" s="231" t="s">
         <v>413</v>
       </c>
-      <c r="E26" s="373" t="s">
+      <c r="E26" s="314" t="s">
         <v>400</v>
       </c>
       <c r="F26" s="231" t="s">
         <v>417</v>
       </c>
-      <c r="G26" s="339">
+      <c r="G26" s="302">
         <v>0.15</v>
       </c>
       <c r="H26" s="105"/>
@@ -26827,24 +26827,24 @@
       <c r="O26" s="96">
         <v>0</v>
       </c>
-      <c r="P26" s="351">
+      <c r="P26" s="319">
         <f>IF(SUM(O26:O30)&gt;=1,$G$26,0)</f>
         <v>0</v>
       </c>
       <c r="Q26" s="204"/>
     </row>
     <row r="27" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A27" s="336"/>
-      <c r="B27" s="361"/>
-      <c r="C27" s="361"/>
+      <c r="A27" s="299"/>
+      <c r="B27" s="343"/>
+      <c r="C27" s="343"/>
       <c r="D27" s="103" t="s">
         <v>374</v>
       </c>
-      <c r="E27" s="374"/>
+      <c r="E27" s="315"/>
       <c r="F27" s="103" t="s">
         <v>375</v>
       </c>
-      <c r="G27" s="340"/>
+      <c r="G27" s="303"/>
       <c r="H27" s="105"/>
       <c r="I27" s="233">
         <v>0.01</v>
@@ -26863,21 +26863,21 @@
       <c r="O27" s="96">
         <v>0</v>
       </c>
-      <c r="P27" s="352"/>
+      <c r="P27" s="320"/>
       <c r="Q27" s="204"/>
     </row>
     <row r="28" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A28" s="336"/>
-      <c r="B28" s="361"/>
-      <c r="C28" s="361"/>
+      <c r="A28" s="299"/>
+      <c r="B28" s="343"/>
+      <c r="C28" s="343"/>
       <c r="D28" s="103" t="s">
         <v>376</v>
       </c>
-      <c r="E28" s="374"/>
+      <c r="E28" s="315"/>
       <c r="F28" s="103" t="s">
         <v>377</v>
       </c>
-      <c r="G28" s="340"/>
+      <c r="G28" s="303"/>
       <c r="H28" s="105"/>
       <c r="I28" s="105">
         <v>0.01</v>
@@ -26896,21 +26896,21 @@
       <c r="O28" s="96">
         <v>0</v>
       </c>
-      <c r="P28" s="352"/>
+      <c r="P28" s="320"/>
       <c r="Q28" s="204"/>
     </row>
     <row r="29" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A29" s="336"/>
-      <c r="B29" s="361"/>
-      <c r="C29" s="361"/>
+      <c r="A29" s="299"/>
+      <c r="B29" s="343"/>
+      <c r="C29" s="343"/>
       <c r="D29" s="231" t="s">
         <v>482</v>
       </c>
-      <c r="E29" s="374"/>
+      <c r="E29" s="315"/>
       <c r="F29" s="231" t="s">
         <v>483</v>
       </c>
-      <c r="G29" s="340"/>
+      <c r="G29" s="303"/>
       <c r="H29" s="105"/>
       <c r="I29" s="234" t="s">
         <v>481</v>
@@ -26927,21 +26927,21 @@
       <c r="O29" s="96">
         <v>0</v>
       </c>
-      <c r="P29" s="352"/>
+      <c r="P29" s="320"/>
       <c r="Q29" s="204"/>
     </row>
     <row r="30" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A30" s="337"/>
-      <c r="B30" s="362"/>
-      <c r="C30" s="362"/>
+      <c r="A30" s="300"/>
+      <c r="B30" s="344"/>
+      <c r="C30" s="344"/>
       <c r="D30" s="231" t="s">
         <v>484</v>
       </c>
-      <c r="E30" s="375"/>
+      <c r="E30" s="316"/>
       <c r="F30" s="103" t="s">
         <v>375</v>
       </c>
-      <c r="G30" s="341"/>
+      <c r="G30" s="304"/>
       <c r="H30" s="105"/>
       <c r="I30" s="233">
         <v>0.01</v>
@@ -26958,29 +26958,29 @@
       <c r="O30" s="96">
         <v>0</v>
       </c>
-      <c r="P30" s="353"/>
+      <c r="P30" s="321"/>
       <c r="Q30" s="204"/>
     </row>
     <row r="31" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A31" s="354" t="s">
+      <c r="A31" s="329" t="s">
         <v>291</v>
       </c>
-      <c r="B31" s="363" t="s">
+      <c r="B31" s="331" t="s">
         <v>378</v>
       </c>
-      <c r="C31" s="363" t="s">
+      <c r="C31" s="331" t="s">
         <v>379</v>
       </c>
       <c r="D31" s="108" t="s">
         <v>380</v>
       </c>
-      <c r="E31" s="357" t="s">
+      <c r="E31" s="335" t="s">
         <v>401</v>
       </c>
       <c r="F31" s="108" t="s">
         <v>381</v>
       </c>
-      <c r="G31" s="345">
+      <c r="G31" s="317">
         <v>0.15</v>
       </c>
       <c r="H31" s="74"/>
@@ -27005,24 +27005,24 @@
       <c r="O31" s="79">
         <v>0</v>
       </c>
-      <c r="P31" s="348">
+      <c r="P31" s="309">
         <f>IF(SUM(O31:O34)&gt;=1,$G$31,0)</f>
         <v>0</v>
       </c>
       <c r="Q31" s="207"/>
     </row>
     <row r="32" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A32" s="355"/>
-      <c r="B32" s="364"/>
-      <c r="C32" s="364"/>
+      <c r="A32" s="340"/>
+      <c r="B32" s="345"/>
+      <c r="C32" s="345"/>
       <c r="D32" s="108" t="s">
         <v>284</v>
       </c>
-      <c r="E32" s="358"/>
+      <c r="E32" s="341"/>
       <c r="F32" s="108" t="s">
         <v>385</v>
       </c>
-      <c r="G32" s="346"/>
+      <c r="G32" s="328"/>
       <c r="H32" s="107"/>
       <c r="I32" s="107" t="s">
         <v>382</v>
@@ -27045,21 +27045,21 @@
       <c r="O32" s="79">
         <v>0</v>
       </c>
-      <c r="P32" s="349"/>
+      <c r="P32" s="310"/>
       <c r="Q32" s="204"/>
     </row>
     <row r="33" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A33" s="355"/>
-      <c r="B33" s="365"/>
-      <c r="C33" s="365"/>
+      <c r="A33" s="340"/>
+      <c r="B33" s="332"/>
+      <c r="C33" s="332"/>
       <c r="D33" s="203" t="s">
         <v>733</v>
       </c>
-      <c r="E33" s="358"/>
+      <c r="E33" s="341"/>
       <c r="F33" s="203" t="s">
         <v>719</v>
       </c>
-      <c r="G33" s="346"/>
+      <c r="G33" s="328"/>
       <c r="H33" s="107"/>
       <c r="I33" s="235" t="s">
         <v>720</v>
@@ -27076,11 +27076,11 @@
       <c r="O33" s="79">
         <v>0</v>
       </c>
-      <c r="P33" s="349"/>
+      <c r="P33" s="310"/>
       <c r="Q33" s="207"/>
     </row>
     <row r="34" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A34" s="356"/>
+      <c r="A34" s="330"/>
       <c r="B34" s="108" t="s">
         <v>386</v>
       </c>
@@ -27090,11 +27090,11 @@
       <c r="D34" s="108" t="s">
         <v>285</v>
       </c>
-      <c r="E34" s="359"/>
+      <c r="E34" s="336"/>
       <c r="F34" s="108" t="s">
         <v>387</v>
       </c>
-      <c r="G34" s="347"/>
+      <c r="G34" s="318"/>
       <c r="H34" s="107"/>
       <c r="I34" s="76" t="s">
         <v>388</v>
@@ -27117,7 +27117,7 @@
       <c r="O34" s="79">
         <v>0</v>
       </c>
-      <c r="P34" s="350"/>
+      <c r="P34" s="311"/>
       <c r="Q34" s="204"/>
     </row>
     <row r="35" spans="1:17" ht="86.1" customHeight="1">
@@ -27175,42 +27175,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="P17:P19"/>
-    <mergeCell ref="L1:N5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="E26:E30"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="G26:G30"/>
-    <mergeCell ref="P26:P30"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:H2"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="E20:E23"/>
-    <mergeCell ref="G20:G23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="A1:B5"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G10:G16"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="E10:E16"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="E31:E34"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
     <mergeCell ref="G31:G34"/>
     <mergeCell ref="P31:P34"/>
     <mergeCell ref="A6:A8"/>
@@ -27227,6 +27191,42 @@
     <mergeCell ref="P24:P25"/>
     <mergeCell ref="P10:P16"/>
     <mergeCell ref="A31:A34"/>
+    <mergeCell ref="E31:E34"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="E10:E16"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:H2"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="G20:G23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="A1:B5"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G10:G16"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="P17:P19"/>
+    <mergeCell ref="L1:N5"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="E26:E30"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="G26:G30"/>
+    <mergeCell ref="P26:P30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -27315,46 +27315,46 @@
       <c r="A2" s="6"/>
       <c r="B2" s="40"/>
       <c r="C2" s="36"/>
-      <c r="D2" s="260" t="s">
+      <c r="D2" s="362" t="s">
         <v>304</v>
       </c>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="261"/>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="261"/>
-      <c r="O2" s="261"/>
-      <c r="P2" s="261"/>
-      <c r="Q2" s="261"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="261"/>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="261"/>
-      <c r="X2" s="261"/>
-      <c r="Y2" s="261"/>
-      <c r="Z2" s="261"/>
-      <c r="AA2" s="261"/>
-      <c r="AB2" s="261"/>
-      <c r="AC2" s="261"/>
-      <c r="AD2" s="261"/>
-      <c r="AE2" s="261"/>
-      <c r="AF2" s="261"/>
-      <c r="AG2" s="261"/>
-      <c r="AH2" s="261"/>
-      <c r="AI2" s="261"/>
-      <c r="AJ2" s="261"/>
-      <c r="AK2" s="261"/>
-      <c r="AL2" s="261"/>
-      <c r="AM2" s="261"/>
-      <c r="AN2" s="261"/>
-      <c r="AO2" s="252" t="s">
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
+      <c r="M2" s="363"/>
+      <c r="N2" s="363"/>
+      <c r="O2" s="363"/>
+      <c r="P2" s="363"/>
+      <c r="Q2" s="363"/>
+      <c r="R2" s="363"/>
+      <c r="S2" s="363"/>
+      <c r="T2" s="363"/>
+      <c r="U2" s="363"/>
+      <c r="V2" s="363"/>
+      <c r="W2" s="363"/>
+      <c r="X2" s="363"/>
+      <c r="Y2" s="363"/>
+      <c r="Z2" s="363"/>
+      <c r="AA2" s="363"/>
+      <c r="AB2" s="363"/>
+      <c r="AC2" s="363"/>
+      <c r="AD2" s="363"/>
+      <c r="AE2" s="363"/>
+      <c r="AF2" s="363"/>
+      <c r="AG2" s="363"/>
+      <c r="AH2" s="363"/>
+      <c r="AI2" s="363"/>
+      <c r="AJ2" s="363"/>
+      <c r="AK2" s="363"/>
+      <c r="AL2" s="363"/>
+      <c r="AM2" s="363"/>
+      <c r="AN2" s="363"/>
+      <c r="AO2" s="354" t="s">
         <v>747</v>
       </c>
     </row>
@@ -27362,130 +27362,130 @@
       <c r="A3" s="6"/>
       <c r="B3" s="35"/>
       <c r="C3" s="37"/>
-      <c r="D3" s="262"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="263"/>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
-      <c r="M3" s="263"/>
-      <c r="N3" s="263"/>
-      <c r="O3" s="263"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="263"/>
-      <c r="S3" s="263"/>
-      <c r="T3" s="263"/>
-      <c r="U3" s="263"/>
-      <c r="V3" s="263"/>
-      <c r="W3" s="263"/>
-      <c r="X3" s="263"/>
-      <c r="Y3" s="263"/>
-      <c r="Z3" s="263"/>
-      <c r="AA3" s="263"/>
-      <c r="AB3" s="263"/>
-      <c r="AC3" s="263"/>
-      <c r="AD3" s="263"/>
-      <c r="AE3" s="263"/>
-      <c r="AF3" s="263"/>
-      <c r="AG3" s="263"/>
-      <c r="AH3" s="263"/>
-      <c r="AI3" s="263"/>
-      <c r="AJ3" s="263"/>
-      <c r="AK3" s="263"/>
-      <c r="AL3" s="263"/>
-      <c r="AM3" s="263"/>
-      <c r="AN3" s="263"/>
-      <c r="AO3" s="253"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="365"/>
+      <c r="F3" s="365"/>
+      <c r="G3" s="365"/>
+      <c r="H3" s="365"/>
+      <c r="I3" s="365"/>
+      <c r="J3" s="365"/>
+      <c r="K3" s="365"/>
+      <c r="L3" s="365"/>
+      <c r="M3" s="365"/>
+      <c r="N3" s="365"/>
+      <c r="O3" s="365"/>
+      <c r="P3" s="365"/>
+      <c r="Q3" s="365"/>
+      <c r="R3" s="365"/>
+      <c r="S3" s="365"/>
+      <c r="T3" s="365"/>
+      <c r="U3" s="365"/>
+      <c r="V3" s="365"/>
+      <c r="W3" s="365"/>
+      <c r="X3" s="365"/>
+      <c r="Y3" s="365"/>
+      <c r="Z3" s="365"/>
+      <c r="AA3" s="365"/>
+      <c r="AB3" s="365"/>
+      <c r="AC3" s="365"/>
+      <c r="AD3" s="365"/>
+      <c r="AE3" s="365"/>
+      <c r="AF3" s="365"/>
+      <c r="AG3" s="365"/>
+      <c r="AH3" s="365"/>
+      <c r="AI3" s="365"/>
+      <c r="AJ3" s="365"/>
+      <c r="AK3" s="365"/>
+      <c r="AL3" s="365"/>
+      <c r="AM3" s="365"/>
+      <c r="AN3" s="365"/>
+      <c r="AO3" s="355"/>
     </row>
     <row r="4" spans="1:41" ht="15.75" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="35"/>
       <c r="C4" s="37"/>
-      <c r="D4" s="262"/>
-      <c r="E4" s="263"/>
-      <c r="F4" s="263"/>
-      <c r="G4" s="263"/>
-      <c r="H4" s="263"/>
-      <c r="I4" s="263"/>
-      <c r="J4" s="263"/>
-      <c r="K4" s="263"/>
-      <c r="L4" s="263"/>
-      <c r="M4" s="263"/>
-      <c r="N4" s="263"/>
-      <c r="O4" s="263"/>
-      <c r="P4" s="263"/>
-      <c r="Q4" s="263"/>
-      <c r="R4" s="263"/>
-      <c r="S4" s="263"/>
-      <c r="T4" s="263"/>
-      <c r="U4" s="263"/>
-      <c r="V4" s="263"/>
-      <c r="W4" s="263"/>
-      <c r="X4" s="263"/>
-      <c r="Y4" s="263"/>
-      <c r="Z4" s="263"/>
-      <c r="AA4" s="263"/>
-      <c r="AB4" s="263"/>
-      <c r="AC4" s="263"/>
-      <c r="AD4" s="263"/>
-      <c r="AE4" s="263"/>
-      <c r="AF4" s="263"/>
-      <c r="AG4" s="263"/>
-      <c r="AH4" s="263"/>
-      <c r="AI4" s="263"/>
-      <c r="AJ4" s="263"/>
-      <c r="AK4" s="263"/>
-      <c r="AL4" s="263"/>
-      <c r="AM4" s="263"/>
-      <c r="AN4" s="263"/>
-      <c r="AO4" s="253"/>
+      <c r="D4" s="364"/>
+      <c r="E4" s="365"/>
+      <c r="F4" s="365"/>
+      <c r="G4" s="365"/>
+      <c r="H4" s="365"/>
+      <c r="I4" s="365"/>
+      <c r="J4" s="365"/>
+      <c r="K4" s="365"/>
+      <c r="L4" s="365"/>
+      <c r="M4" s="365"/>
+      <c r="N4" s="365"/>
+      <c r="O4" s="365"/>
+      <c r="P4" s="365"/>
+      <c r="Q4" s="365"/>
+      <c r="R4" s="365"/>
+      <c r="S4" s="365"/>
+      <c r="T4" s="365"/>
+      <c r="U4" s="365"/>
+      <c r="V4" s="365"/>
+      <c r="W4" s="365"/>
+      <c r="X4" s="365"/>
+      <c r="Y4" s="365"/>
+      <c r="Z4" s="365"/>
+      <c r="AA4" s="365"/>
+      <c r="AB4" s="365"/>
+      <c r="AC4" s="365"/>
+      <c r="AD4" s="365"/>
+      <c r="AE4" s="365"/>
+      <c r="AF4" s="365"/>
+      <c r="AG4" s="365"/>
+      <c r="AH4" s="365"/>
+      <c r="AI4" s="365"/>
+      <c r="AJ4" s="365"/>
+      <c r="AK4" s="365"/>
+      <c r="AL4" s="365"/>
+      <c r="AM4" s="365"/>
+      <c r="AN4" s="365"/>
+      <c r="AO4" s="355"/>
     </row>
     <row r="5" spans="1:41" ht="15.75" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="35"/>
       <c r="C5" s="38"/>
-      <c r="D5" s="264"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
-      <c r="M5" s="266"/>
-      <c r="N5" s="265"/>
-      <c r="O5" s="265"/>
-      <c r="P5" s="266"/>
-      <c r="Q5" s="266"/>
-      <c r="R5" s="266"/>
-      <c r="S5" s="266"/>
-      <c r="T5" s="266"/>
-      <c r="U5" s="266"/>
-      <c r="V5" s="266"/>
-      <c r="W5" s="266"/>
-      <c r="X5" s="266"/>
-      <c r="Y5" s="266"/>
-      <c r="Z5" s="266"/>
-      <c r="AA5" s="266"/>
-      <c r="AB5" s="265"/>
-      <c r="AC5" s="265"/>
-      <c r="AD5" s="265"/>
-      <c r="AE5" s="265"/>
-      <c r="AF5" s="266"/>
-      <c r="AG5" s="266"/>
-      <c r="AH5" s="266"/>
-      <c r="AI5" s="266"/>
-      <c r="AJ5" s="266"/>
-      <c r="AK5" s="266"/>
-      <c r="AL5" s="266"/>
-      <c r="AM5" s="266"/>
-      <c r="AN5" s="266"/>
-      <c r="AO5" s="254"/>
+      <c r="D5" s="366"/>
+      <c r="E5" s="367"/>
+      <c r="F5" s="367"/>
+      <c r="G5" s="368"/>
+      <c r="H5" s="368"/>
+      <c r="I5" s="368"/>
+      <c r="J5" s="368"/>
+      <c r="K5" s="368"/>
+      <c r="L5" s="368"/>
+      <c r="M5" s="368"/>
+      <c r="N5" s="367"/>
+      <c r="O5" s="367"/>
+      <c r="P5" s="368"/>
+      <c r="Q5" s="368"/>
+      <c r="R5" s="368"/>
+      <c r="S5" s="368"/>
+      <c r="T5" s="368"/>
+      <c r="U5" s="368"/>
+      <c r="V5" s="368"/>
+      <c r="W5" s="368"/>
+      <c r="X5" s="368"/>
+      <c r="Y5" s="368"/>
+      <c r="Z5" s="368"/>
+      <c r="AA5" s="368"/>
+      <c r="AB5" s="367"/>
+      <c r="AC5" s="367"/>
+      <c r="AD5" s="367"/>
+      <c r="AE5" s="367"/>
+      <c r="AF5" s="368"/>
+      <c r="AG5" s="368"/>
+      <c r="AH5" s="368"/>
+      <c r="AI5" s="368"/>
+      <c r="AJ5" s="368"/>
+      <c r="AK5" s="368"/>
+      <c r="AL5" s="368"/>
+      <c r="AM5" s="368"/>
+      <c r="AN5" s="368"/>
+      <c r="AO5" s="356"/>
     </row>
     <row r="6" spans="1:41" ht="18.75" customHeight="1">
       <c r="A6" s="6"/>
@@ -27779,111 +27779,111 @@
     <row r="13" spans="1:41" s="25" customFormat="1" ht="47.45" customHeight="1">
       <c r="A13" s="24"/>
       <c r="B13" s="24"/>
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="379" t="s">
         <v>256</v>
       </c>
-      <c r="D13" s="241" t="s">
+      <c r="D13" s="379" t="s">
         <v>257</v>
       </c>
-      <c r="E13" s="241" t="s">
+      <c r="E13" s="379" t="s">
         <v>258</v>
       </c>
-      <c r="F13" s="241" t="s">
+      <c r="F13" s="379" t="s">
         <v>259</v>
       </c>
-      <c r="G13" s="242" t="s">
+      <c r="G13" s="380" t="s">
         <v>296</v>
       </c>
-      <c r="H13" s="243"/>
-      <c r="I13" s="239" t="s">
+      <c r="H13" s="381"/>
+      <c r="I13" s="377" t="s">
         <v>297</v>
       </c>
-      <c r="J13" s="240"/>
-      <c r="K13" s="240"/>
-      <c r="L13" s="240"/>
-      <c r="M13" s="240"/>
-      <c r="N13" s="240"/>
-      <c r="O13" s="240"/>
-      <c r="P13" s="240"/>
-      <c r="Q13" s="240"/>
-      <c r="R13" s="240"/>
-      <c r="S13" s="240"/>
-      <c r="T13" s="240"/>
-      <c r="U13" s="240"/>
-      <c r="V13" s="240"/>
-      <c r="W13" s="240"/>
-      <c r="X13" s="240"/>
-      <c r="Y13" s="240"/>
-      <c r="Z13" s="240"/>
-      <c r="AA13" s="240"/>
-      <c r="AB13" s="240"/>
-      <c r="AC13" s="240"/>
-      <c r="AD13" s="240"/>
-      <c r="AE13" s="240"/>
-      <c r="AF13" s="267" t="s">
+      <c r="J13" s="378"/>
+      <c r="K13" s="378"/>
+      <c r="L13" s="378"/>
+      <c r="M13" s="378"/>
+      <c r="N13" s="378"/>
+      <c r="O13" s="378"/>
+      <c r="P13" s="378"/>
+      <c r="Q13" s="378"/>
+      <c r="R13" s="378"/>
+      <c r="S13" s="378"/>
+      <c r="T13" s="378"/>
+      <c r="U13" s="378"/>
+      <c r="V13" s="378"/>
+      <c r="W13" s="378"/>
+      <c r="X13" s="378"/>
+      <c r="Y13" s="378"/>
+      <c r="Z13" s="378"/>
+      <c r="AA13" s="378"/>
+      <c r="AB13" s="378"/>
+      <c r="AC13" s="378"/>
+      <c r="AD13" s="378"/>
+      <c r="AE13" s="378"/>
+      <c r="AF13" s="369" t="s">
         <v>298</v>
       </c>
-      <c r="AG13" s="267"/>
-      <c r="AH13" s="267"/>
-      <c r="AI13" s="267"/>
-      <c r="AJ13" s="267"/>
-      <c r="AK13" s="267"/>
-      <c r="AL13" s="267"/>
-      <c r="AM13" s="267"/>
-      <c r="AN13" s="267"/>
+      <c r="AG13" s="369"/>
+      <c r="AH13" s="369"/>
+      <c r="AI13" s="369"/>
+      <c r="AJ13" s="369"/>
+      <c r="AK13" s="369"/>
+      <c r="AL13" s="369"/>
+      <c r="AM13" s="369"/>
+      <c r="AN13" s="369"/>
       <c r="AO13" s="26"/>
     </row>
     <row r="14" spans="1:41" s="25" customFormat="1" ht="47.45" customHeight="1">
       <c r="A14" s="24"/>
       <c r="B14" s="24"/>
-      <c r="C14" s="241"/>
-      <c r="D14" s="241"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="241"/>
-      <c r="G14" s="270" t="s">
+      <c r="C14" s="379"/>
+      <c r="D14" s="379"/>
+      <c r="E14" s="379"/>
+      <c r="F14" s="379"/>
+      <c r="G14" s="372" t="s">
         <v>300</v>
       </c>
-      <c r="H14" s="270" t="s">
+      <c r="H14" s="372" t="s">
         <v>308</v>
       </c>
-      <c r="I14" s="247" t="s">
+      <c r="I14" s="349" t="s">
         <v>313</v>
       </c>
-      <c r="J14" s="248"/>
-      <c r="K14" s="248"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="248"/>
-      <c r="N14" s="248"/>
-      <c r="O14" s="247" t="s">
+      <c r="J14" s="350"/>
+      <c r="K14" s="350"/>
+      <c r="L14" s="350"/>
+      <c r="M14" s="350"/>
+      <c r="N14" s="350"/>
+      <c r="O14" s="349" t="s">
         <v>314</v>
       </c>
-      <c r="P14" s="248"/>
-      <c r="Q14" s="248"/>
-      <c r="R14" s="248"/>
-      <c r="S14" s="248"/>
-      <c r="T14" s="248"/>
-      <c r="U14" s="248"/>
-      <c r="V14" s="248"/>
-      <c r="W14" s="248"/>
-      <c r="X14" s="248"/>
-      <c r="Y14" s="248"/>
-      <c r="Z14" s="248"/>
-      <c r="AA14" s="248"/>
-      <c r="AB14" s="248"/>
-      <c r="AC14" s="248"/>
-      <c r="AD14" s="248"/>
-      <c r="AE14" s="248"/>
-      <c r="AF14" s="268" t="s">
+      <c r="P14" s="350"/>
+      <c r="Q14" s="350"/>
+      <c r="R14" s="350"/>
+      <c r="S14" s="350"/>
+      <c r="T14" s="350"/>
+      <c r="U14" s="350"/>
+      <c r="V14" s="350"/>
+      <c r="W14" s="350"/>
+      <c r="X14" s="350"/>
+      <c r="Y14" s="350"/>
+      <c r="Z14" s="350"/>
+      <c r="AA14" s="350"/>
+      <c r="AB14" s="350"/>
+      <c r="AC14" s="350"/>
+      <c r="AD14" s="350"/>
+      <c r="AE14" s="350"/>
+      <c r="AF14" s="370" t="s">
         <v>299</v>
       </c>
-      <c r="AG14" s="268"/>
-      <c r="AH14" s="268"/>
-      <c r="AI14" s="268"/>
-      <c r="AJ14" s="268"/>
-      <c r="AK14" s="268"/>
-      <c r="AL14" s="268"/>
-      <c r="AM14" s="268"/>
-      <c r="AN14" s="269" t="s">
+      <c r="AG14" s="370"/>
+      <c r="AH14" s="370"/>
+      <c r="AI14" s="370"/>
+      <c r="AJ14" s="370"/>
+      <c r="AK14" s="370"/>
+      <c r="AL14" s="370"/>
+      <c r="AM14" s="370"/>
+      <c r="AN14" s="371" t="s">
         <v>305</v>
       </c>
       <c r="AO14" s="26"/>
@@ -27891,61 +27891,61 @@
     <row r="15" spans="1:41" ht="34.5" customHeight="1">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
-      <c r="C15" s="241"/>
-      <c r="D15" s="241"/>
-      <c r="E15" s="241"/>
-      <c r="F15" s="241"/>
-      <c r="G15" s="271"/>
-      <c r="H15" s="272"/>
-      <c r="I15" s="249"/>
-      <c r="J15" s="250"/>
-      <c r="K15" s="250"/>
-      <c r="L15" s="250"/>
-      <c r="M15" s="250"/>
-      <c r="N15" s="250"/>
-      <c r="O15" s="249"/>
-      <c r="P15" s="250"/>
-      <c r="Q15" s="250"/>
-      <c r="R15" s="250"/>
-      <c r="S15" s="250"/>
-      <c r="T15" s="250"/>
-      <c r="U15" s="250"/>
-      <c r="V15" s="250"/>
-      <c r="W15" s="250"/>
-      <c r="X15" s="250"/>
-      <c r="Y15" s="250"/>
-      <c r="Z15" s="250"/>
-      <c r="AA15" s="250"/>
-      <c r="AB15" s="250"/>
-      <c r="AC15" s="250"/>
-      <c r="AD15" s="250"/>
-      <c r="AE15" s="250"/>
-      <c r="AF15" s="257" t="s">
+      <c r="C15" s="379"/>
+      <c r="D15" s="379"/>
+      <c r="E15" s="379"/>
+      <c r="F15" s="379"/>
+      <c r="G15" s="373"/>
+      <c r="H15" s="374"/>
+      <c r="I15" s="351"/>
+      <c r="J15" s="352"/>
+      <c r="K15" s="352"/>
+      <c r="L15" s="352"/>
+      <c r="M15" s="352"/>
+      <c r="N15" s="352"/>
+      <c r="O15" s="351"/>
+      <c r="P15" s="352"/>
+      <c r="Q15" s="352"/>
+      <c r="R15" s="352"/>
+      <c r="S15" s="352"/>
+      <c r="T15" s="352"/>
+      <c r="U15" s="352"/>
+      <c r="V15" s="352"/>
+      <c r="W15" s="352"/>
+      <c r="X15" s="352"/>
+      <c r="Y15" s="352"/>
+      <c r="Z15" s="352"/>
+      <c r="AA15" s="352"/>
+      <c r="AB15" s="352"/>
+      <c r="AC15" s="352"/>
+      <c r="AD15" s="352"/>
+      <c r="AE15" s="352"/>
+      <c r="AF15" s="359" t="s">
         <v>294</v>
       </c>
-      <c r="AG15" s="258"/>
-      <c r="AH15" s="259"/>
-      <c r="AI15" s="257" t="s">
+      <c r="AG15" s="360"/>
+      <c r="AH15" s="361"/>
+      <c r="AI15" s="359" t="s">
         <v>295</v>
       </c>
-      <c r="AJ15" s="258"/>
-      <c r="AK15" s="259"/>
-      <c r="AL15" s="273" t="s">
+      <c r="AJ15" s="360"/>
+      <c r="AK15" s="361"/>
+      <c r="AL15" s="375" t="s">
         <v>726</v>
       </c>
-      <c r="AM15" s="274"/>
-      <c r="AN15" s="269"/>
-      <c r="AO15" s="255" t="s">
+      <c r="AM15" s="376"/>
+      <c r="AN15" s="371"/>
+      <c r="AO15" s="357" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:41" ht="43.5" customHeight="1">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
-      <c r="C16" s="241"/>
-      <c r="D16" s="241"/>
-      <c r="E16" s="241"/>
-      <c r="F16" s="241"/>
+      <c r="C16" s="379"/>
+      <c r="D16" s="379"/>
+      <c r="E16" s="379"/>
+      <c r="F16" s="379"/>
       <c r="G16" s="34" t="s">
         <v>301</v>
       </c>
@@ -28048,7 +28048,7 @@
       <c r="AN16" s="42" t="s">
         <v>307</v>
       </c>
-      <c r="AO16" s="256"/>
+      <c r="AO16" s="358"/>
     </row>
     <row r="17" spans="1:41" ht="18.75" customHeight="1">
       <c r="A17" s="6"/>
@@ -28163,7 +28163,7 @@
         <v>0.93</v>
       </c>
       <c r="AF17" s="32">
-        <f>'P3.1.2 (KPI Senior)'!M9</f>
+        <f>'P3.1.1 (KPI Senior)'!M9</f>
         <v>0</v>
       </c>
       <c r="AG17" s="32">
@@ -28313,7 +28313,7 @@
         <v>0.87</v>
       </c>
       <c r="AF18" s="32">
-        <f>'P3.1.2 (KPI Senior)'!M10</f>
+        <f>'P3.1.1 (KPI Senior)'!M10</f>
         <v>0</v>
       </c>
       <c r="AG18" s="32">
@@ -28454,33 +28454,33 @@
       <c r="F21" s="197" t="s">
         <v>259</v>
       </c>
-      <c r="G21" s="251" t="s">
+      <c r="G21" s="353" t="s">
         <v>274</v>
       </c>
-      <c r="H21" s="251"/>
-      <c r="I21" s="251"/>
-      <c r="J21" s="251"/>
-      <c r="K21" s="251"/>
-      <c r="L21" s="251"/>
-      <c r="M21" s="251"/>
-      <c r="N21" s="251"/>
-      <c r="O21" s="251"/>
-      <c r="P21" s="251"/>
-      <c r="Q21" s="251"/>
-      <c r="R21" s="251"/>
-      <c r="S21" s="251"/>
-      <c r="T21" s="251"/>
-      <c r="U21" s="251"/>
-      <c r="V21" s="251"/>
-      <c r="W21" s="251"/>
-      <c r="X21" s="251"/>
-      <c r="Y21" s="251"/>
-      <c r="Z21" s="251"/>
-      <c r="AA21" s="251"/>
-      <c r="AB21" s="251"/>
-      <c r="AC21" s="251"/>
-      <c r="AD21" s="251"/>
-      <c r="AE21" s="251"/>
+      <c r="H21" s="353"/>
+      <c r="I21" s="353"/>
+      <c r="J21" s="353"/>
+      <c r="K21" s="353"/>
+      <c r="L21" s="353"/>
+      <c r="M21" s="353"/>
+      <c r="N21" s="353"/>
+      <c r="O21" s="353"/>
+      <c r="P21" s="353"/>
+      <c r="Q21" s="353"/>
+      <c r="R21" s="353"/>
+      <c r="S21" s="353"/>
+      <c r="T21" s="353"/>
+      <c r="U21" s="353"/>
+      <c r="V21" s="353"/>
+      <c r="W21" s="353"/>
+      <c r="X21" s="353"/>
+      <c r="Y21" s="353"/>
+      <c r="Z21" s="353"/>
+      <c r="AA21" s="353"/>
+      <c r="AB21" s="353"/>
+      <c r="AC21" s="353"/>
+      <c r="AD21" s="353"/>
+      <c r="AE21" s="353"/>
       <c r="AF21" s="6"/>
       <c r="AG21" s="6"/>
       <c r="AH21" s="6"/>
@@ -28507,31 +28507,31 @@
       <c r="F22" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="G22" s="251"/>
-      <c r="H22" s="251"/>
-      <c r="I22" s="251"/>
-      <c r="J22" s="251"/>
-      <c r="K22" s="251"/>
-      <c r="L22" s="251"/>
-      <c r="M22" s="251"/>
-      <c r="N22" s="251"/>
-      <c r="O22" s="251"/>
-      <c r="P22" s="251"/>
-      <c r="Q22" s="251"/>
-      <c r="R22" s="251"/>
-      <c r="S22" s="251"/>
-      <c r="T22" s="251"/>
-      <c r="U22" s="251"/>
-      <c r="V22" s="251"/>
-      <c r="W22" s="251"/>
-      <c r="X22" s="251"/>
-      <c r="Y22" s="251"/>
-      <c r="Z22" s="251"/>
-      <c r="AA22" s="251"/>
-      <c r="AB22" s="251"/>
-      <c r="AC22" s="251"/>
-      <c r="AD22" s="251"/>
-      <c r="AE22" s="251"/>
+      <c r="G22" s="353"/>
+      <c r="H22" s="353"/>
+      <c r="I22" s="353"/>
+      <c r="J22" s="353"/>
+      <c r="K22" s="353"/>
+      <c r="L22" s="353"/>
+      <c r="M22" s="353"/>
+      <c r="N22" s="353"/>
+      <c r="O22" s="353"/>
+      <c r="P22" s="353"/>
+      <c r="Q22" s="353"/>
+      <c r="R22" s="353"/>
+      <c r="S22" s="353"/>
+      <c r="T22" s="353"/>
+      <c r="U22" s="353"/>
+      <c r="V22" s="353"/>
+      <c r="W22" s="353"/>
+      <c r="X22" s="353"/>
+      <c r="Y22" s="353"/>
+      <c r="Z22" s="353"/>
+      <c r="AA22" s="353"/>
+      <c r="AB22" s="353"/>
+      <c r="AC22" s="353"/>
+      <c r="AD22" s="353"/>
+      <c r="AE22" s="353"/>
       <c r="AF22" s="6"/>
       <c r="AG22" s="6"/>
       <c r="AH22" s="6"/>
@@ -28558,31 +28558,31 @@
       <c r="F23" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="G23" s="244"/>
-      <c r="H23" s="245"/>
-      <c r="I23" s="245"/>
-      <c r="J23" s="245"/>
-      <c r="K23" s="245"/>
-      <c r="L23" s="245"/>
-      <c r="M23" s="245"/>
-      <c r="N23" s="245"/>
-      <c r="O23" s="245"/>
-      <c r="P23" s="245"/>
-      <c r="Q23" s="245"/>
-      <c r="R23" s="245"/>
-      <c r="S23" s="245"/>
-      <c r="T23" s="245"/>
-      <c r="U23" s="245"/>
-      <c r="V23" s="245"/>
-      <c r="W23" s="245"/>
-      <c r="X23" s="245"/>
-      <c r="Y23" s="245"/>
-      <c r="Z23" s="245"/>
-      <c r="AA23" s="245"/>
-      <c r="AB23" s="245"/>
-      <c r="AC23" s="245"/>
-      <c r="AD23" s="245"/>
-      <c r="AE23" s="246"/>
+      <c r="G23" s="346"/>
+      <c r="H23" s="347"/>
+      <c r="I23" s="347"/>
+      <c r="J23" s="347"/>
+      <c r="K23" s="347"/>
+      <c r="L23" s="347"/>
+      <c r="M23" s="347"/>
+      <c r="N23" s="347"/>
+      <c r="O23" s="347"/>
+      <c r="P23" s="347"/>
+      <c r="Q23" s="347"/>
+      <c r="R23" s="347"/>
+      <c r="S23" s="347"/>
+      <c r="T23" s="347"/>
+      <c r="U23" s="347"/>
+      <c r="V23" s="347"/>
+      <c r="W23" s="347"/>
+      <c r="X23" s="347"/>
+      <c r="Y23" s="347"/>
+      <c r="Z23" s="347"/>
+      <c r="AA23" s="347"/>
+      <c r="AB23" s="347"/>
+      <c r="AC23" s="347"/>
+      <c r="AD23" s="347"/>
+      <c r="AE23" s="348"/>
       <c r="AF23" s="6"/>
       <c r="AG23" s="6"/>
       <c r="AH23" s="6"/>
@@ -37364,6 +37364,12 @@
     <row r="989" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="I13:AE13"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="F13:F16"/>
+    <mergeCell ref="G13:H13"/>
     <mergeCell ref="G23:AE23"/>
     <mergeCell ref="I14:N15"/>
     <mergeCell ref="G22:AE22"/>
@@ -37380,12 +37386,6 @@
     <mergeCell ref="O14:AE15"/>
     <mergeCell ref="G21:AE21"/>
     <mergeCell ref="AL15:AM15"/>
-    <mergeCell ref="I13:AE13"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="E13:E16"/>
-    <mergeCell ref="F13:F16"/>
-    <mergeCell ref="G13:H13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
